--- a/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>GENI</t>
   </si>
@@ -656,86 +656,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -748,47 +748,50 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>127200</v>
+      </c>
+      <c r="E8" s="3">
         <v>101700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>86800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>97200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>105300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>78700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>71100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>85900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>84000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>69100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>55800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>53700</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,8 +804,8 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
@@ -810,47 +813,50 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>116700</v>
+      </c>
+      <c r="E9" s="3">
         <v>77400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>62200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>87700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>102200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>72800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>61800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>101400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>109400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>86400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>240200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>40100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -872,47 +878,50 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E10" s="3">
         <v>24300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-15500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-25400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-17300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-184400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13600</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -934,8 +943,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -958,47 +970,48 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E12" s="3">
         <v>6100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3300</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1020,8 +1033,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1082,47 +1098,50 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1500</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1135,8 +1154,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1144,8 +1163,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1206,8 +1228,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1227,55 +1252,56 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>161600</v>
+      </c>
+      <c r="E17" s="3">
         <v>110600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>94700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>120300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>150200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>112000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>110800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>150900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>160300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>133900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>485000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>56800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
+      <c r="R17" s="3">
+        <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
@@ -1289,47 +1315,50 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-23100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-44900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-33300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-39700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-65000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-76300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-64800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-429200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1351,8 +1380,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1375,47 +1407,48 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-81500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>25000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>35300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>25800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-34600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2500</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1437,47 +1470,50 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E21" s="3">
         <v>7600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-109200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-21700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-47200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-50900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-451500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4600</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1499,22 +1535,25 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>400</v>
       </c>
       <c r="H22" s="3">
         <v>400</v>
@@ -1525,11 +1564,11 @@
       <c r="J22" s="3">
         <v>400</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3">
+        <v>400</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1561,55 +1600,58 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-24500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-126700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-39600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-64600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-70500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-463800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5600</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-300</v>
       </c>
       <c r="P23" s="3">
         <v>-300</v>
       </c>
       <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
@@ -1623,52 +1665,55 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-11300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
@@ -1676,8 +1721,8 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1685,8 +1730,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1747,55 +1795,58 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-127700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-40200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-53300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-70000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-464200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5300</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-300</v>
       </c>
       <c r="P26" s="3">
         <v>-300</v>
       </c>
       <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
@@ -1809,55 +1860,58 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-127700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-40200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-64600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-70000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-464200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5300</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-300</v>
       </c>
       <c r="P27" s="3">
         <v>-300</v>
       </c>
       <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="R27" s="3">
+        <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
@@ -1871,8 +1925,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1933,8 +1990,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1995,8 +2055,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2057,8 +2120,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2119,47 +2185,50 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E32" s="3">
         <v>1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>81500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-25000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-35300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-25800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>34600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2500</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2181,55 +2250,58 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-127700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-40200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-64600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-70000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-464200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5300</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-300</v>
       </c>
       <c r="P33" s="3">
         <v>-300</v>
       </c>
       <c r="Q33" s="3">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="R33" s="3">
+        <v>0</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
@@ -2243,8 +2315,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2305,55 +2380,58 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-127700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-40200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-64600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-70000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-464200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5300</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-300</v>
       </c>
       <c r="P35" s="3">
         <v>-300</v>
       </c>
       <c r="Q35" s="3">
-        <v>0</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="R35" s="3">
+        <v>0</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
@@ -2367,61 +2445,64 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2434,8 +2515,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2458,8 +2542,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2482,55 +2567,56 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E41" s="3">
         <v>92000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>89800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>94400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>122700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>116900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>138500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>174200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>222400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>234200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>275300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1000</v>
-      </c>
-      <c r="O41" s="3">
-        <v>1500</v>
       </c>
       <c r="P41" s="3">
         <v>1500</v>
       </c>
       <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="R41" s="3">
+        <v>0</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
@@ -2544,8 +2630,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2606,44 +2695,47 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>109900</v>
+      </c>
+      <c r="E43" s="3">
         <v>105600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>99300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>82400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>73200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>69200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>56900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>89600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>77300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>66000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>57800</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2659,8 +2751,8 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -2668,49 +2760,52 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>400</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E44" s="3">
         <v>400</v>
       </c>
       <c r="F44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G44" s="3">
         <v>300</v>
       </c>
       <c r="H44" s="3">
+        <v>300</v>
+      </c>
+      <c r="I44" s="3">
         <v>400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>300</v>
-      </c>
-      <c r="J44" s="3">
-        <v>500</v>
       </c>
       <c r="K44" s="3">
         <v>500</v>
       </c>
       <c r="L44" s="3">
+        <v>500</v>
+      </c>
+      <c r="M44" s="3">
         <v>600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>400</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2730,52 +2825,55 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E45" s="3">
         <v>50100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>32700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>41300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>40300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>51700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>37800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>29700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>24400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
-      </c>
-      <c r="O45" s="3">
-        <v>200</v>
       </c>
       <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
+      <c r="Q45" s="3">
+        <v>200</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
@@ -2792,55 +2890,58 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>244800</v>
+      </c>
+      <c r="E46" s="3">
         <v>248100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>222200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>218400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>236500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>238100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>233500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>294000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>324700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>333900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>344600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1400</v>
-      </c>
-      <c r="O46" s="3">
-        <v>1700</v>
       </c>
       <c r="P46" s="3">
         <v>1700</v>
       </c>
       <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
+        <v>1700</v>
+      </c>
+      <c r="R46" s="3">
+        <v>0</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
@@ -2854,52 +2955,55 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E47" s="3">
         <v>31700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>32400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>31800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>32800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>29400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>29300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>31100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
         <v>276100</v>
-      </c>
-      <c r="O47" s="3">
-        <v>276000</v>
       </c>
       <c r="P47" s="3">
         <v>276000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>276000</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2916,44 +3020,47 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E48" s="3">
         <v>19500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17700</v>
-      </c>
-      <c r="F48" s="3">
-        <v>19300</v>
       </c>
       <c r="G48" s="3">
         <v>19300</v>
       </c>
       <c r="H48" s="3">
+        <v>19300</v>
+      </c>
+      <c r="I48" s="3">
         <v>11800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10400</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2969,8 +3076,8 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -2978,44 +3085,47 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>455700</v>
+      </c>
+      <c r="E49" s="3">
         <v>447200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>469500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>462000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>459100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>428900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>473600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>516700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>537600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>542500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>523100</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3031,8 +3141,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3040,8 +3150,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3102,8 +3215,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3164,56 +3280,59 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E52" s="3">
         <v>25800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>28000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3226,8 +3345,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3288,56 +3410,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>775700</v>
+      </c>
+      <c r="E54" s="3">
         <v>772200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>768800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>757900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>773300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>734000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>778000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>859700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>887100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>896900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>890000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>277400</v>
-      </c>
-      <c r="O54" s="3">
-        <v>277800</v>
       </c>
       <c r="P54" s="3">
         <v>277800</v>
       </c>
       <c r="Q54" s="3">
+        <v>277800</v>
+      </c>
+      <c r="R54" s="3">
         <v>200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3475,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3374,8 +3502,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3398,43 +3527,44 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E57" s="3">
         <v>43700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>23600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>21400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>33100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>30600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>20700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11800</v>
-      </c>
-      <c r="N57" s="3">
-        <v>200</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
@@ -3443,10 +3573,10 @@
         <v>200</v>
       </c>
       <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="R57" s="3">
+        <v>0</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
@@ -3460,43 +3590,46 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E58" s="3">
         <v>7300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
@@ -3504,12 +3637,12 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3522,56 +3655,59 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E59" s="3">
         <v>123700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>117800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>116200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>130600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>102500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>98100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>105800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>132900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>135000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>205700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
-      </c>
-      <c r="O59" s="3">
-        <v>300</v>
       </c>
       <c r="P59" s="3">
         <v>300</v>
       </c>
       <c r="Q59" s="3">
+        <v>300</v>
+      </c>
+      <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3584,43 +3720,46 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>182900</v>
+      </c>
+      <c r="E60" s="3">
         <v>174700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>148800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>144800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>171100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>140300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>118400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>134300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>152800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>146300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>217400</v>
-      </c>
-      <c r="N60" s="3">
-        <v>600</v>
       </c>
       <c r="O60" s="3">
         <v>600</v>
@@ -3629,11 +3768,11 @@
         <v>600</v>
       </c>
       <c r="Q60" s="3">
+        <v>600</v>
+      </c>
+      <c r="R60" s="3">
         <v>100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,8 +3785,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3661,19 +3803,19 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>7100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7400</v>
-      </c>
-      <c r="K61" s="3">
-        <v>100</v>
       </c>
       <c r="L61" s="3">
         <v>100</v>
@@ -3682,7 +3824,7 @@
         <v>100</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -3708,43 +3850,46 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E62" s="3">
         <v>20000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>19200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>27000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>28000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>38400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>29900</v>
-      </c>
-      <c r="N62" s="3">
-        <v>9700</v>
       </c>
       <c r="O62" s="3">
         <v>9700</v>
@@ -3752,8 +3897,8 @@
       <c r="P62" s="3">
         <v>9700</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3">
+        <v>9700</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
@@ -3770,8 +3915,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3832,8 +3980,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3894,8 +4045,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3956,43 +4110,46 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>202700</v>
+      </c>
+      <c r="E66" s="3">
         <v>194800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>167500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>164000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>196500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>161100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>141200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>168700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>180900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>184800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>247400</v>
-      </c>
-      <c r="N66" s="3">
-        <v>10200</v>
       </c>
       <c r="O66" s="3">
         <v>10200</v>
@@ -4001,11 +4158,11 @@
         <v>10200</v>
       </c>
       <c r="Q66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="R66" s="3">
         <v>100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4018,8 +4175,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4042,8 +4202,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4104,8 +4265,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4166,8 +4330,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4228,8 +4395,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4290,55 +4460,58 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1024500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-986000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-974400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-964100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-939000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-811200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-802300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-797500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-757300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-704000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-634100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-600</v>
-      </c>
-      <c r="O72" s="3">
-        <v>-300</v>
       </c>
       <c r="P72" s="3">
         <v>-300</v>
       </c>
       <c r="Q72" s="3">
-        <v>0</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="R72" s="3">
+        <v>0</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
@@ -4352,8 +4525,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4414,8 +4590,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4476,8 +4655,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4538,55 +4720,58 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>573000</v>
+      </c>
+      <c r="E76" s="3">
         <v>577400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>601300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>593900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>576800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>572900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>636800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>691100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>706200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>712100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>642600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>267200</v>
-      </c>
-      <c r="O76" s="3">
-        <v>267500</v>
       </c>
       <c r="P76" s="3">
         <v>267500</v>
       </c>
       <c r="Q76" s="3">
-        <v>0</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
+        <v>267500</v>
+      </c>
+      <c r="R76" s="3">
+        <v>0</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
@@ -4600,8 +4785,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4662,61 +4850,64 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4729,55 +4920,58 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-127700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-40200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-64600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-70000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-464200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5300</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-300</v>
       </c>
       <c r="P81" s="3">
         <v>-300</v>
       </c>
       <c r="Q81" s="3">
-        <v>0</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="R81" s="3">
+        <v>0</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
@@ -4791,8 +4985,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4815,55 +5012,56 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E83" s="3">
         <v>18000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>17100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>17300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>17500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>17400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>19500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -4877,8 +5075,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4939,8 +5140,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5001,8 +5205,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5063,8 +5270,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5125,8 +5335,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5187,55 +5400,58 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E89" s="3">
         <v>13600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-18800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>23100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-25300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-34100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-29900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
@@ -5249,8 +5465,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5273,55 +5492,56 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -5335,8 +5555,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5397,8 +5620,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5459,49 +5685,52 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-35200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-80500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4200</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -5512,8 +5741,8 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -5521,8 +5750,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5545,8 +5777,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5607,8 +5840,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5669,8 +5905,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5731,8 +5970,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5793,8 +6035,11 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5805,11 +6050,11 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -5820,28 +6065,28 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>33400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>375700</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>277600</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
@@ -5855,55 +6100,58 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>18700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-10400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -5917,55 +6165,58 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E102" s="3">
         <v>1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-27500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-24600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-48200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-41100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>264800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1500</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
@@ -5977,6 +6228,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>GENI</t>
   </si>
@@ -656,89 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -751,50 +752,53 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>119700</v>
+      </c>
+      <c r="E8" s="3">
         <v>127200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>101700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>86800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>97200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>105300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>78700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>71100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>85900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>84000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>69100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>55800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>53700</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -807,8 +811,8 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
@@ -816,50 +820,53 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>106900</v>
+      </c>
+      <c r="E9" s="3">
         <v>116700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>77400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>62200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>87700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>102200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>72800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>61800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>101400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>109400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>86400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>240200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>40100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -881,50 +888,53 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E10" s="3">
         <v>10500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-15500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-25400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-17300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-184400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13600</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -946,8 +956,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -971,50 +984,51 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E12" s="3">
         <v>7900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>9800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3300</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1036,8 +1050,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1101,50 +1118,53 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>500</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1500</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1157,8 +1177,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1166,8 +1186,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1231,8 +1254,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1253,58 +1279,59 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E17" s="3">
         <v>161600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>110600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>94700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>120300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>150200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>112000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>110800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>150900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>160300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>133900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>485000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>56800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
@@ -1318,50 +1345,53 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-34400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-23100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-44900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-33300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-39700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-65000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-76300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-64800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-429200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3100</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1383,8 +1413,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1408,50 +1441,51 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-4500</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-81500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>25000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>35300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>25800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>11700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-34600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2500</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1473,50 +1507,53 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-14600</v>
+        <v>-3200</v>
       </c>
       <c r="E21" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="F21" s="3">
         <v>7600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-109200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-21700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-47200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-50900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-451500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4600</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1538,25 +1575,28 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>100</v>
       </c>
       <c r="E22" s="3">
+        <v>200</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>400</v>
       </c>
       <c r="I22" s="3">
         <v>400</v>
@@ -1567,11 +1607,11 @@
       <c r="K22" s="3">
         <v>400</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3">
+        <v>400</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1603,58 +1643,61 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-38900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-126700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-39600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-64600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-70500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-463800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5600</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-300</v>
       </c>
       <c r="Q23" s="3">
         <v>-300</v>
       </c>
       <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
@@ -1668,55 +1711,58 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-11300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
@@ -1724,8 +1770,8 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1733,8 +1779,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1798,58 +1847,61 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-38500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-25200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-127700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-40200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-53300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-70000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-464200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5300</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-300</v>
       </c>
       <c r="Q26" s="3">
         <v>-300</v>
       </c>
       <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
@@ -1863,58 +1915,61 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-38500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-25200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-127700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-40200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-64600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-70000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-464200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5300</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-300</v>
       </c>
       <c r="Q27" s="3">
         <v>-300</v>
       </c>
       <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="S27" s="3">
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
@@ -1928,8 +1983,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1993,8 +2051,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2058,8 +2119,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2123,8 +2187,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2188,50 +2255,53 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F32" s="3">
         <v>1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>81500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-25000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-35300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-25800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-11700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>34600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2500</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2253,58 +2323,61 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-38500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-25200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-127700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-40200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-64600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-70000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-464200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5300</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-300</v>
       </c>
       <c r="Q33" s="3">
         <v>-300</v>
       </c>
       <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
@@ -2318,8 +2391,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2383,58 +2459,61 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-38500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-25200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-127700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-40200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-64600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-70000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-464200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5300</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-300</v>
       </c>
       <c r="Q35" s="3">
         <v>-300</v>
       </c>
       <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="S35" s="3">
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
@@ -2448,64 +2527,67 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2518,8 +2600,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2543,8 +2628,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2568,58 +2654,59 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E41" s="3">
         <v>100300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>92000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>89800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>94400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>122700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>116900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>138500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>174200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>222400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>234200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>275300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1000</v>
-      </c>
-      <c r="P41" s="3">
-        <v>1500</v>
       </c>
       <c r="Q41" s="3">
         <v>1500</v>
       </c>
       <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="S41" s="3">
+        <v>0</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
@@ -2633,8 +2720,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2698,47 +2788,50 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>109900</v>
+        <v>131900</v>
       </c>
       <c r="E43" s="3">
+        <v>110100</v>
+      </c>
+      <c r="F43" s="3">
         <v>105600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>99300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>82400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>73200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>69200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>56900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>89600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>77300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>66000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>57800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2754,8 +2847,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -2763,52 +2856,55 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>300</v>
       </c>
       <c r="E44" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F44" s="3">
         <v>400</v>
       </c>
       <c r="G44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H44" s="3">
         <v>300</v>
       </c>
       <c r="I44" s="3">
+        <v>300</v>
+      </c>
+      <c r="J44" s="3">
         <v>400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>300</v>
-      </c>
-      <c r="K44" s="3">
-        <v>500</v>
       </c>
       <c r="L44" s="3">
         <v>500</v>
       </c>
       <c r="M44" s="3">
+        <v>500</v>
+      </c>
+      <c r="N44" s="3">
         <v>600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>400</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2828,55 +2924,58 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>34600</v>
+        <v>29500</v>
       </c>
       <c r="E45" s="3">
+        <v>34000</v>
+      </c>
+      <c r="F45" s="3">
         <v>50100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>32700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>41300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>40300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>51700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>37800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
-      </c>
-      <c r="P45" s="3">
-        <v>200</v>
       </c>
       <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
+      <c r="R45" s="3">
+        <v>200</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
@@ -2893,58 +2992,61 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>229200</v>
+      </c>
+      <c r="E46" s="3">
         <v>244800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>248100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>222200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>218400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>236500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>238100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>233500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>294000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>324700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>333900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>344600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1400</v>
-      </c>
-      <c r="P46" s="3">
-        <v>1700</v>
       </c>
       <c r="Q46" s="3">
         <v>1700</v>
       </c>
       <c r="R46" s="3">
-        <v>0</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
+        <v>1700</v>
+      </c>
+      <c r="S46" s="3">
+        <v>0</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
@@ -2958,55 +3060,58 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>26400</v>
+        <v>27000</v>
       </c>
       <c r="E47" s="3">
+        <v>29900</v>
+      </c>
+      <c r="F47" s="3">
         <v>31700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>32400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>31800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>32800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>29400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>29300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>31100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>276100</v>
-      </c>
-      <c r="P47" s="3">
-        <v>276000</v>
       </c>
       <c r="Q47" s="3">
         <v>276000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>276000</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -3023,47 +3128,50 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E48" s="3">
         <v>18600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17700</v>
-      </c>
-      <c r="G48" s="3">
-        <v>19300</v>
       </c>
       <c r="H48" s="3">
         <v>19300</v>
       </c>
       <c r="I48" s="3">
+        <v>19300</v>
+      </c>
+      <c r="J48" s="3">
         <v>11800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10400</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3079,8 +3187,8 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3088,47 +3196,50 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>443100</v>
+      </c>
+      <c r="E49" s="3">
         <v>455700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>447200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>469500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>462000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>459100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>428900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>473600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>516700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>537600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>542500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>523100</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3144,8 +3255,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3153,8 +3264,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3218,8 +3332,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3283,59 +3400,62 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>30300</v>
+        <v>26600</v>
       </c>
       <c r="E52" s="3">
+        <v>26800</v>
+      </c>
+      <c r="F52" s="3">
         <v>25800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,8 +3468,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3413,59 +3536,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>745400</v>
+      </c>
+      <c r="E54" s="3">
         <v>775700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>772200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>768800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>757900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>773300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>734000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>778000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>859700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>887100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>896900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>890000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>277400</v>
-      </c>
-      <c r="P54" s="3">
-        <v>277800</v>
       </c>
       <c r="Q54" s="3">
         <v>277800</v>
       </c>
       <c r="R54" s="3">
+        <v>277800</v>
+      </c>
+      <c r="S54" s="3">
         <v>200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3478,8 +3604,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3503,8 +3632,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3528,46 +3658,47 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E57" s="3">
         <v>57400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>43700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>33100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>20700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11800</v>
-      </c>
-      <c r="O57" s="3">
-        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
@@ -3576,10 +3707,10 @@
         <v>200</v>
       </c>
       <c r="R57" s="3">
-        <v>0</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3593,46 +3724,49 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>7600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7700</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
@@ -3640,12 +3774,12 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3658,59 +3792,62 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>123500</v>
+      </c>
+      <c r="E59" s="3">
         <v>118000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>123700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>117800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>116200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>130600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>102500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>98100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>105800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>132900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>135000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>205700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>300</v>
       </c>
       <c r="Q59" s="3">
         <v>300</v>
       </c>
       <c r="R59" s="3">
+        <v>300</v>
+      </c>
+      <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,46 +3860,49 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>174900</v>
+      </c>
+      <c r="E60" s="3">
         <v>182900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>174700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>148800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>144800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>171100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>140300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>118400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>134300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>152800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>146300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>217400</v>
-      </c>
-      <c r="O60" s="3">
-        <v>600</v>
       </c>
       <c r="P60" s="3">
         <v>600</v>
@@ -3771,11 +3911,11 @@
         <v>600</v>
       </c>
       <c r="R60" s="3">
+        <v>600</v>
+      </c>
+      <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3788,8 +3928,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3806,19 +3949,19 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>7100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7400</v>
-      </c>
-      <c r="L61" s="3">
-        <v>100</v>
       </c>
       <c r="M61" s="3">
         <v>100</v>
@@ -3827,7 +3970,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -3853,46 +3996,49 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E62" s="3">
         <v>19800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>19200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>27000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>28000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>38400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>29900</v>
-      </c>
-      <c r="O62" s="3">
-        <v>9700</v>
       </c>
       <c r="P62" s="3">
         <v>9700</v>
@@ -3900,8 +4046,8 @@
       <c r="Q62" s="3">
         <v>9700</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>9700</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
@@ -3918,8 +4064,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3983,8 +4132,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4048,8 +4200,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4113,46 +4268,49 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>194900</v>
+      </c>
+      <c r="E66" s="3">
         <v>202700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>194800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>167500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>164000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>196500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>161100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>141200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>168700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>180900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>184800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>247400</v>
-      </c>
-      <c r="O66" s="3">
-        <v>10200</v>
       </c>
       <c r="P66" s="3">
         <v>10200</v>
@@ -4161,11 +4319,11 @@
         <v>10200</v>
       </c>
       <c r="R66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="S66" s="3">
         <v>100</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4178,8 +4336,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4203,8 +4364,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4268,8 +4430,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4333,8 +4498,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4398,8 +4566,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4463,58 +4634,61 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1050000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1024500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-986000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-974400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-964100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-939000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-811200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-802300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-797500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-757300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-704000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-634100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-600</v>
-      </c>
-      <c r="P72" s="3">
-        <v>-300</v>
       </c>
       <c r="Q72" s="3">
         <v>-300</v>
       </c>
       <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
@@ -4528,8 +4702,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4593,8 +4770,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4658,8 +4838,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4723,58 +4906,61 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>550500</v>
+      </c>
+      <c r="E76" s="3">
         <v>573000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>577400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>601300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>593900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>576800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>572900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>636800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>691100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>706200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>712100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>642600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>267200</v>
-      </c>
-      <c r="P76" s="3">
-        <v>267500</v>
       </c>
       <c r="Q76" s="3">
         <v>267500</v>
       </c>
       <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+        <v>267500</v>
+      </c>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
@@ -4788,8 +4974,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4853,64 +5042,67 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4923,58 +5115,61 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-38500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-25200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-127700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-40200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-64600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-70000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-464200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5300</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-300</v>
       </c>
       <c r="Q81" s="3">
         <v>-300</v>
       </c>
       <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="S81" s="3">
+        <v>0</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
@@ -4988,8 +5183,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5013,58 +5211,59 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E83" s="3">
         <v>24300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>17300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>17100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>17300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>17500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>17400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>19500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -5078,8 +5277,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5143,8 +5345,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5208,8 +5413,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5273,8 +5481,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5338,8 +5549,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5403,58 +5617,61 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E89" s="3">
         <v>24000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-18800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>23100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-25300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-34100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-29900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
@@ -5468,8 +5685,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5493,58 +5713,59 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -5558,8 +5779,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5623,8 +5847,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5688,52 +5915,55 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-80500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4200</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5744,8 +5974,8 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -5753,8 +5983,11 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5778,8 +6011,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5843,8 +6077,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5908,8 +6145,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5973,8 +6213,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6038,13 +6281,16 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-7600</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -6053,11 +6299,11 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -6068,28 +6314,28 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>33400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>375700</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>277600</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
@@ -6103,58 +6349,61 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>18700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-10400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -6168,58 +6417,61 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E102" s="3">
         <v>9400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-16300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-24600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-48200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-41100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>264800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1500</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
@@ -6231,6 +6483,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -755,53 +756,56 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E8" s="3">
         <v>119700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>127200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>101700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>86800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>97200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>105300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>78700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>71100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>85900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>84000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>69100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>55800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>53700</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -814,8 +818,8 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -823,53 +827,56 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E9" s="3">
         <v>106900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>116700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>77400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>62200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>87700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>102200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>72800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>61800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>101400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>109400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>86400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>240200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>40100</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -891,53 +898,56 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E10" s="3">
         <v>12800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-15500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-25400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-17300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-184400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13600</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,8 +969,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,53 +998,54 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E12" s="3">
         <v>6600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3300</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1067,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,53 +1138,56 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E14" s="3">
         <v>500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1500</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1180,8 +1200,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1189,8 +1209,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1257,8 +1280,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,61 +1306,62 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>116400</v>
+      </c>
+      <c r="E17" s="3">
         <v>144000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>161600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>110600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>94700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>120300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>150200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>112000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>110800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>150900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>160300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>133900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>485000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>56800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+      <c r="T17" s="3">
+        <v>0</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
@@ -1348,53 +1375,56 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-24300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-34400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-23100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-44900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-33300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-39700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-65000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-76300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-64800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-429200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1416,8 +1446,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,53 +1475,54 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-1900</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-81500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>25000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>35300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>25800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-34600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1510,53 +1544,56 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-109200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-21700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-47200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-50900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-451500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,28 +1615,31 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>400</v>
       </c>
       <c r="J22" s="3">
         <v>400</v>
@@ -1610,11 +1650,11 @@
       <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3">
+        <v>400</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1646,61 +1686,64 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-38900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-126700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-39600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-64600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-70500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-463800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5600</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-300</v>
       </c>
       <c r="R23" s="3">
         <v>-300</v>
       </c>
       <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
@@ -1714,58 +1757,61 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-11300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
@@ -1773,8 +1819,8 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1782,8 +1828,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,61 +1899,64 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-38500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-127700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-40200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-53300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-70000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-464200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5300</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-300</v>
       </c>
       <c r="R26" s="3">
         <v>-300</v>
       </c>
       <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="T26" s="3">
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
@@ -1918,61 +1970,64 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-25500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-38500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-127700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-40200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-64600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-70000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-464200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5300</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-300</v>
       </c>
       <c r="R27" s="3">
         <v>-300</v>
       </c>
       <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="T27" s="3">
+        <v>0</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
@@ -1986,8 +2041,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,8 +2112,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2122,8 +2183,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2254,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,53 +2325,56 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>81500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-25000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-35300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-25800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>34600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2500</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2326,61 +2396,64 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-25500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-38500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-127700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-40200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-64600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-70000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-464200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5300</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-300</v>
       </c>
       <c r="R33" s="3">
         <v>-300</v>
       </c>
       <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="T33" s="3">
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
@@ -2394,8 +2467,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,61 +2538,64 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-25500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-38500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-127700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-40200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-64600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-70000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-464200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5300</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-300</v>
       </c>
       <c r="R35" s="3">
         <v>-300</v>
       </c>
       <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="T35" s="3">
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
@@ -2530,67 +2609,70 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2603,8 +2685,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2714,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,61 +2741,62 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>67700</v>
+      </c>
+      <c r="E41" s="3">
         <v>67500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>100300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>92000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>89800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>94400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>122700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>116900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>138500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>174200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>222400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>234200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>275300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>1500</v>
       </c>
       <c r="R41" s="3">
         <v>1500</v>
       </c>
       <c r="S41" s="3">
-        <v>0</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="T41" s="3">
+        <v>0</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
@@ -2723,8 +2810,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2791,50 +2881,53 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>98400</v>
+      </c>
+      <c r="E43" s="3">
         <v>131900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>110100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>105600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>99300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>82400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>73200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>69200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>56900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>89600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>77300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>66000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>57800</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2850,8 +2943,8 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -2859,55 +2952,58 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E44" s="3">
         <v>300</v>
       </c>
       <c r="F44" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G44" s="3">
         <v>400</v>
       </c>
       <c r="H44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I44" s="3">
         <v>300</v>
       </c>
       <c r="J44" s="3">
+        <v>300</v>
+      </c>
+      <c r="K44" s="3">
         <v>400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>300</v>
-      </c>
-      <c r="L44" s="3">
-        <v>500</v>
       </c>
       <c r="M44" s="3">
         <v>500</v>
       </c>
       <c r="N44" s="3">
+        <v>500</v>
+      </c>
+      <c r="O44" s="3">
         <v>600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>400</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -2927,58 +3023,61 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E45" s="3">
         <v>29500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>34000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>50100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>32700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>41300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>40300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>51700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>37800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>29700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>24400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>200</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>200</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -2995,61 +3094,64 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>222500</v>
+      </c>
+      <c r="E46" s="3">
         <v>229200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>244800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>248100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>222200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>218400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>236500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>238100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>233500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>294000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>324700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>333900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>344600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>1700</v>
       </c>
       <c r="R46" s="3">
         <v>1700</v>
       </c>
       <c r="S46" s="3">
-        <v>0</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
+        <v>1700</v>
+      </c>
+      <c r="T46" s="3">
+        <v>0</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
@@ -3063,58 +3165,61 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E47" s="3">
         <v>27000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>29900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>31700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>32400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>31800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>32800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>29400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>29300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>31100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>276100</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>276000</v>
       </c>
       <c r="R47" s="3">
         <v>276000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>276000</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -3131,50 +3236,53 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E48" s="3">
         <v>19600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17700</v>
-      </c>
-      <c r="H48" s="3">
-        <v>19300</v>
       </c>
       <c r="I48" s="3">
         <v>19300</v>
       </c>
       <c r="J48" s="3">
+        <v>19300</v>
+      </c>
+      <c r="K48" s="3">
         <v>11800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10400</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3190,8 +3298,8 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3199,50 +3307,53 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>440500</v>
+      </c>
+      <c r="E49" s="3">
         <v>443100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>455700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>447200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>469500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>462000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>459100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>428900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>473600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>516700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>537600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>542500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>523100</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3258,8 +3369,8 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3267,8 +3378,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3449,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,62 +3520,65 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E52" s="3">
         <v>26600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>27000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12000</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3591,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,62 +3662,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>716000</v>
+      </c>
+      <c r="E54" s="3">
         <v>745400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>775700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>772200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>768800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>757900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>773300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>734000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>778000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>859700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>887100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>896900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>890000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>277400</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>277800</v>
       </c>
       <c r="R54" s="3">
         <v>277800</v>
       </c>
       <c r="S54" s="3">
+        <v>277800</v>
+      </c>
+      <c r="T54" s="3">
         <v>200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3733,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3762,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,49 +3789,50 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E57" s="3">
         <v>51400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>57400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>43700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>33100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>30600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>20700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>19900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11800</v>
-      </c>
-      <c r="P57" s="3">
-        <v>200</v>
       </c>
       <c r="Q57" s="3">
         <v>200</v>
@@ -3710,10 +3841,10 @@
         <v>200</v>
       </c>
       <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="T57" s="3">
+        <v>0</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
@@ -3727,8 +3858,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3736,40 +3870,40 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>7600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7700</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
@@ -3777,12 +3911,12 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3795,62 +3929,65 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E59" s="3">
         <v>123500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>118000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>123700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>117800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>116200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>130600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>102500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>98100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>105800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>132900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>135000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>205700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>400</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>300</v>
       </c>
       <c r="R59" s="3">
         <v>300</v>
       </c>
       <c r="S59" s="3">
+        <v>300</v>
+      </c>
+      <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,49 +4000,52 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>144500</v>
+      </c>
+      <c r="E60" s="3">
         <v>174900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>182900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>174700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>148800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>144800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>171100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>140300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>118400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>134300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>152800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>146300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>217400</v>
-      </c>
-      <c r="P60" s="3">
-        <v>600</v>
       </c>
       <c r="Q60" s="3">
         <v>600</v>
@@ -3914,11 +4054,11 @@
         <v>600</v>
       </c>
       <c r="S60" s="3">
+        <v>600</v>
+      </c>
+      <c r="T60" s="3">
         <v>100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,8 +4071,11 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3952,19 +4095,19 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>7100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7400</v>
-      </c>
-      <c r="M61" s="3">
-        <v>100</v>
       </c>
       <c r="N61" s="3">
         <v>100</v>
@@ -3973,7 +4116,7 @@
         <v>100</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -3999,49 +4142,52 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E62" s="3">
         <v>20000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>19800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>19200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>27000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>28000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>38400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>29900</v>
-      </c>
-      <c r="P62" s="3">
-        <v>9700</v>
       </c>
       <c r="Q62" s="3">
         <v>9700</v>
@@ -4049,8 +4195,8 @@
       <c r="R62" s="3">
         <v>9700</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="S62" s="3">
+        <v>9700</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -4067,8 +4213,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4284,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4355,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,49 +4426,52 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>163600</v>
+      </c>
+      <c r="E66" s="3">
         <v>194900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>202700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>194800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>167500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>164000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>196500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>161100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>141200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>168700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>180900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>184800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>247400</v>
-      </c>
-      <c r="P66" s="3">
-        <v>10200</v>
       </c>
       <c r="Q66" s="3">
         <v>10200</v>
@@ -4322,11 +4480,11 @@
         <v>10200</v>
       </c>
       <c r="S66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="T66" s="3">
         <v>100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4339,8 +4497,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4526,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4595,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,8 +4666,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4569,8 +4737,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,61 +4808,64 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1071800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1050000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1024500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-986000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-974400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-964100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-939000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-811200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-802300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-797500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-757300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-704000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-634100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-600</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-300</v>
       </c>
       <c r="R72" s="3">
         <v>-300</v>
       </c>
       <c r="S72" s="3">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="T72" s="3">
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
@@ -4705,8 +4879,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +4950,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5021,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,61 +5092,64 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>552400</v>
+      </c>
+      <c r="E76" s="3">
         <v>550500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>573000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>577400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>601300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>593900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>576800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>572900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>636800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>691100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>706200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>712100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>642600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>267200</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>267500</v>
       </c>
       <c r="R76" s="3">
         <v>267500</v>
       </c>
       <c r="S76" s="3">
-        <v>0</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
+        <v>267500</v>
+      </c>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
@@ -4977,8 +5163,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,67 +5234,70 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5118,61 +5310,64 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-25500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-38500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-127700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-40200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-64600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-70000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-464200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5300</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-300</v>
       </c>
       <c r="R81" s="3">
         <v>-300</v>
       </c>
       <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="T81" s="3">
+        <v>0</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
@@ -5186,8 +5381,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,61 +5410,62 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E83" s="3">
         <v>21100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>24300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>17700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>17300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>17100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>16700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>17300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>17500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>17400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>19500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -5280,8 +5479,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5550,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5621,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5692,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5763,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,61 +5834,64 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-14600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>24000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-18800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>23100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-25300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-34100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-29900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
@@ -5688,8 +5905,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,61 +5934,62 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -5782,8 +6003,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6074,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,55 +6145,58 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-35200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-80500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5977,8 +6207,8 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -5986,8 +6216,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,8 +6245,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6080,8 +6314,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6385,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6456,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,17 +6527,20 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7600</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
@@ -6302,11 +6548,11 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
@@ -6317,28 +6563,28 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>33400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>375700</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>277600</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
@@ -6352,61 +6598,64 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>18700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -6420,61 +6669,64 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-33000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-27500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-24600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-48200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-41100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>264800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1500</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
@@ -6486,6 +6738,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
   <si>
     <t>GENI</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -759,56 +760,59 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>120200</v>
+      </c>
+      <c r="E8" s="3">
         <v>95400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>119700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>127200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>101700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>86800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>97200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>105300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>78700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>71100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>85900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>84000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>69100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>55800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>53700</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -821,8 +825,8 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
@@ -830,56 +834,59 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E9" s="3">
         <v>67100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>106900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>116700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>77400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>62200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>87700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>102200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>72800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>61800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>101400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>109400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>86400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>240200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>40100</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -901,56 +908,59 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>28300</v>
+        <v>40100</v>
       </c>
       <c r="E10" s="3">
-        <v>12800</v>
+        <v>28400</v>
       </c>
       <c r="F10" s="3">
+        <v>12900</v>
+      </c>
+      <c r="G10" s="3">
         <v>10500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24300</v>
       </c>
-      <c r="H10" s="3">
-        <v>24600</v>
-      </c>
       <c r="I10" s="3">
+        <v>24700</v>
+      </c>
+      <c r="J10" s="3">
         <v>9500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-15500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-25400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-17300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-184400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13600</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -972,8 +982,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -999,56 +1012,57 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E12" s="3">
         <v>7200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="H12" s="3">
+        <v>6100</v>
+      </c>
+      <c r="I12" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="K12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="L12" s="3">
+        <v>8100</v>
+      </c>
+      <c r="M12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="N12" s="3">
+        <v>7400</v>
+      </c>
+      <c r="O12" s="3">
         <v>6600</v>
       </c>
-      <c r="F12" s="3">
-        <v>7900</v>
-      </c>
-      <c r="G12" s="3">
-        <v>6100</v>
-      </c>
-      <c r="H12" s="3">
-        <v>5800</v>
-      </c>
-      <c r="I12" s="3">
-        <v>6300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>6700</v>
-      </c>
-      <c r="K12" s="3">
-        <v>8100</v>
-      </c>
-      <c r="L12" s="3">
-        <v>7700</v>
-      </c>
-      <c r="M12" s="3">
-        <v>7400</v>
-      </c>
-      <c r="N12" s="3">
-        <v>6600</v>
-      </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3300</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1070,8 +1084,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1141,56 +1158,59 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3">
         <v>1600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3">
-        <v>300</v>
-      </c>
       <c r="G14" s="3">
+        <v>11900</v>
+      </c>
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="H14" s="3">
-        <v>500</v>
-      </c>
       <c r="I14" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="J14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K14" s="3">
         <v>1500</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1203,8 +1223,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1212,31 +1232,34 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>8900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>30200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>11900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1283,8 +1306,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1307,64 +1333,65 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>116400</v>
+        <v>125800</v>
       </c>
       <c r="E17" s="3">
-        <v>144000</v>
+        <v>114800</v>
       </c>
       <c r="F17" s="3">
-        <v>161600</v>
+        <v>143500</v>
       </c>
       <c r="G17" s="3">
-        <v>110600</v>
+        <v>161200</v>
       </c>
       <c r="H17" s="3">
-        <v>94700</v>
+        <v>109800</v>
       </c>
       <c r="I17" s="3">
-        <v>120300</v>
+        <v>94200</v>
       </c>
       <c r="J17" s="3">
+        <v>119400</v>
+      </c>
+      <c r="K17" s="3">
         <v>150200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>112000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>110800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>150900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>160300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>133900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>485000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>56800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
+      <c r="U17" s="3">
+        <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
@@ -1378,56 +1405,59 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-21000</v>
+        <v>-5600</v>
       </c>
       <c r="E18" s="3">
-        <v>-24300</v>
+        <v>-19400</v>
       </c>
       <c r="F18" s="3">
-        <v>-34400</v>
+        <v>-23800</v>
       </c>
       <c r="G18" s="3">
-        <v>-8900</v>
+        <v>-34100</v>
       </c>
       <c r="H18" s="3">
-        <v>-7900</v>
+        <v>-8100</v>
       </c>
       <c r="I18" s="3">
-        <v>-23100</v>
+        <v>-7300</v>
       </c>
       <c r="J18" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-44900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-33300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-39700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-65000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-76300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-64800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-429200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1449,8 +1479,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,56 +1509,57 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1900</v>
+        <v>-23200</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="F20" s="3">
-        <v>-4300</v>
+        <v>800</v>
       </c>
       <c r="G20" s="3">
-        <v>-1400</v>
+        <v>-6500</v>
       </c>
       <c r="H20" s="3">
-        <v>1700</v>
+        <v>2700</v>
       </c>
       <c r="I20" s="3">
-        <v>-1200</v>
+        <v>-2100</v>
       </c>
       <c r="J20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-81500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>25000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>35300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>25800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>11700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2500</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,56 +1581,59 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-2200</v>
+        <v>26400</v>
       </c>
       <c r="E21" s="3">
-        <v>-3200</v>
+        <v>8400</v>
       </c>
       <c r="F21" s="3">
-        <v>-14400</v>
+        <v>-13000</v>
       </c>
       <c r="G21" s="3">
-        <v>7600</v>
+        <v>-15600</v>
       </c>
       <c r="H21" s="3">
-        <v>11600</v>
+        <v>600</v>
       </c>
       <c r="I21" s="3">
-        <v>-6900</v>
+        <v>18800</v>
       </c>
       <c r="J21" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="K21" s="3">
         <v>-109200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-21700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-47200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-50900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-451500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4600</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,31 +1655,34 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
-        <v>100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>200</v>
-      </c>
-      <c r="I22" s="3">
-        <v>300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>400</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>400</v>
@@ -1653,11 +1693,11 @@
       <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3">
+        <v>400</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1689,64 +1729,67 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-38900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-126700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-39600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-64600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-70500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-463800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5600</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-300</v>
       </c>
       <c r="S23" s="3">
         <v>-300</v>
       </c>
       <c r="T23" s="3">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="U23" s="3">
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
@@ -1760,61 +1803,64 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-11300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-300</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
@@ -1822,8 +1868,8 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -1831,8 +1877,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1902,64 +1951,67 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-38500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-127700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-40200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-53300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-70000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-464200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5300</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-300</v>
       </c>
       <c r="S26" s="3">
         <v>-300</v>
       </c>
       <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="U26" s="3">
+        <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
@@ -1973,64 +2025,67 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-38500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-127700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-40200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-64600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-70000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-464200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5300</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-300</v>
       </c>
       <c r="S27" s="3">
         <v>-300</v>
       </c>
       <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="U27" s="3">
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
@@ -2044,8 +2099,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2115,8 +2173,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2186,8 +2247,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2257,8 +2321,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2328,56 +2395,59 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1900</v>
+        <v>23200</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="F32" s="3">
-        <v>4300</v>
+        <v>-800</v>
       </c>
       <c r="G32" s="3">
-        <v>1400</v>
+        <v>6500</v>
       </c>
       <c r="H32" s="3">
-        <v>-1700</v>
+        <v>-2700</v>
       </c>
       <c r="I32" s="3">
-        <v>1200</v>
+        <v>2100</v>
       </c>
       <c r="J32" s="3">
+        <v>500</v>
+      </c>
+      <c r="K32" s="3">
         <v>81500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-25000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-35300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-25800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-11700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>34600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2500</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2399,64 +2469,67 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-38500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-127700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-40200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-64600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-70000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-464200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5300</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-300</v>
       </c>
       <c r="S33" s="3">
         <v>-300</v>
       </c>
       <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="U33" s="3">
+        <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
@@ -2470,8 +2543,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2541,64 +2617,67 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-38500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-127700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-40200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-64600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-70000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-464200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5300</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-300</v>
       </c>
       <c r="S35" s="3">
         <v>-300</v>
       </c>
       <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="U35" s="3">
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
@@ -2612,70 +2691,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2688,8 +2770,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2715,8 +2800,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2742,64 +2828,65 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E41" s="3">
         <v>67700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>67500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>100300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>92000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>89800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>94400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>122700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>116900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>138500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>174200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>222400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>234200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>275300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1000</v>
-      </c>
-      <c r="R41" s="3">
-        <v>1500</v>
       </c>
       <c r="S41" s="3">
         <v>1500</v>
       </c>
       <c r="T41" s="3">
-        <v>0</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="U41" s="3">
+        <v>0</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
@@ -2813,8 +2900,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2822,10 +2912,10 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -2884,53 +2974,56 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>128800</v>
+      </c>
+      <c r="E43" s="3">
         <v>98400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>131900</v>
       </c>
-      <c r="F43" s="3">
-        <v>110100</v>
-      </c>
       <c r="G43" s="3">
+        <v>116900</v>
+      </c>
+      <c r="H43" s="3">
         <v>105600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>99300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>82400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>73200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>69200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>56900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>89600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>77300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>66000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>57800</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2946,8 +3039,8 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -2955,8 +3048,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2964,49 +3060,49 @@
         <v>500</v>
       </c>
       <c r="E44" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F44" s="3">
         <v>300</v>
       </c>
       <c r="G44" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H44" s="3">
         <v>400</v>
       </c>
       <c r="I44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J44" s="3">
         <v>300</v>
       </c>
       <c r="K44" s="3">
+        <v>300</v>
+      </c>
+      <c r="L44" s="3">
         <v>400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>300</v>
-      </c>
-      <c r="M44" s="3">
-        <v>500</v>
       </c>
       <c r="N44" s="3">
         <v>500</v>
       </c>
       <c r="O44" s="3">
+        <v>500</v>
+      </c>
+      <c r="P44" s="3">
         <v>600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>400</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -3026,61 +3122,64 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>55900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>29500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>34000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>50100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>32700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>41300</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>40300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>51700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>37800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>29700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>24400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>33100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
-      </c>
-      <c r="R45" s="3">
-        <v>200</v>
       </c>
       <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
+      <c r="T45" s="3">
+        <v>200</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
@@ -3097,64 +3196,67 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>224400</v>
+      </c>
+      <c r="E46" s="3">
         <v>222500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>229200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>244800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>248100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>222200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>218400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>236500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>238100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>233500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>294000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>324700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>333900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>344600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1400</v>
-      </c>
-      <c r="R46" s="3">
-        <v>1700</v>
       </c>
       <c r="S46" s="3">
         <v>1700</v>
       </c>
       <c r="T46" s="3">
-        <v>0</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
+        <v>1700</v>
+      </c>
+      <c r="U46" s="3">
+        <v>0</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
@@ -3168,61 +3270,64 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>31000</v>
+        <v>30700</v>
       </c>
       <c r="E47" s="3">
-        <v>27000</v>
+        <v>28900</v>
       </c>
       <c r="F47" s="3">
-        <v>29900</v>
+        <v>25000</v>
       </c>
       <c r="G47" s="3">
-        <v>31700</v>
+        <v>26400</v>
       </c>
       <c r="H47" s="3">
-        <v>32400</v>
+        <v>24700</v>
       </c>
       <c r="I47" s="3">
-        <v>31800</v>
+        <v>24000</v>
       </c>
       <c r="J47" s="3">
+        <v>23000</v>
+      </c>
+      <c r="K47" s="3">
         <v>32800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>29400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>29300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>31100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
         <v>276100</v>
-      </c>
-      <c r="R47" s="3">
-        <v>276000</v>
       </c>
       <c r="S47" s="3">
         <v>276000</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>276000</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
@@ -3239,53 +3344,56 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E48" s="3">
         <v>20600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17700</v>
-      </c>
-      <c r="I48" s="3">
-        <v>19300</v>
       </c>
       <c r="J48" s="3">
         <v>19300</v>
       </c>
       <c r="K48" s="3">
+        <v>19300</v>
+      </c>
+      <c r="L48" s="3">
         <v>11800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10400</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3301,8 +3409,8 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
@@ -3310,53 +3418,56 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>441100</v>
+      </c>
+      <c r="E49" s="3">
         <v>440500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>443100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>455700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>447200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>469500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>462000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>459100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>428900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>473600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>516700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>537600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>542500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>523100</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3372,8 +3483,8 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -3381,8 +3492,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3452,8 +3566,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3523,65 +3640,68 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="E52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F52" s="3">
         <v>26600</v>
       </c>
-      <c r="F52" s="3">
-        <v>26800</v>
-      </c>
       <c r="G52" s="3">
+        <v>28300</v>
+      </c>
+      <c r="H52" s="3">
+        <v>31000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>33500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>33400</v>
+      </c>
+      <c r="K52" s="3">
+        <v>25600</v>
+      </c>
+      <c r="L52" s="3">
         <v>25800</v>
       </c>
-      <c r="H52" s="3">
-        <v>27000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>26300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>25600</v>
-      </c>
-      <c r="K52" s="3">
-        <v>25800</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,8 +3714,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3665,65 +3788,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>724900</v>
+      </c>
+      <c r="E54" s="3">
         <v>716000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>745400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>775700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>772200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>768800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>757900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>773300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>734000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>778000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>859700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>887100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>896900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>890000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>277400</v>
-      </c>
-      <c r="R54" s="3">
-        <v>277800</v>
       </c>
       <c r="S54" s="3">
         <v>277800</v>
       </c>
       <c r="T54" s="3">
+        <v>277800</v>
+      </c>
+      <c r="U54" s="3">
         <v>200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3736,8 +3862,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3763,8 +3892,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3790,52 +3920,53 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E57" s="3">
         <v>39500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>51400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>57400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>43700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>30600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>20700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11800</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>200</v>
       </c>
       <c r="R57" s="3">
         <v>200</v>
@@ -3844,10 +3975,10 @@
         <v>200</v>
       </c>
       <c r="T57" s="3">
-        <v>0</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="U57" s="3">
+        <v>0</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
@@ -3861,52 +3992,55 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="F58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G58" s="3">
+        <v>11200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>10700</v>
+      </c>
+      <c r="I58" s="3">
+        <v>10500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>10500</v>
+      </c>
+      <c r="K58" s="3">
+        <v>7400</v>
+      </c>
+      <c r="L58" s="3">
+        <v>7200</v>
+      </c>
+      <c r="M58" s="3">
         <v>7600</v>
       </c>
-      <c r="G58" s="3">
-        <v>7300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>7400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>7200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>7400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>7200</v>
-      </c>
-      <c r="L58" s="3">
-        <v>7600</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7700</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
@@ -3914,12 +4048,12 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,65 +4066,68 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>105000</v>
+        <v>51600</v>
       </c>
       <c r="E59" s="3">
-        <v>123500</v>
+        <v>50300</v>
       </c>
       <c r="F59" s="3">
-        <v>118000</v>
+        <v>56600</v>
       </c>
       <c r="G59" s="3">
-        <v>123700</v>
+        <v>58000</v>
       </c>
       <c r="H59" s="3">
-        <v>117800</v>
+        <v>54300</v>
       </c>
       <c r="I59" s="3">
-        <v>116200</v>
+        <v>55000</v>
       </c>
       <c r="J59" s="3">
+        <v>52700</v>
+      </c>
+      <c r="K59" s="3">
         <v>130600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>102500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>98100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>105800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>132900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>135000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>205700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>400</v>
-      </c>
-      <c r="R59" s="3">
-        <v>300</v>
       </c>
       <c r="S59" s="3">
         <v>300</v>
       </c>
       <c r="T59" s="3">
+        <v>300</v>
+      </c>
+      <c r="U59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,52 +4140,55 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>149100</v>
+      </c>
+      <c r="E60" s="3">
         <v>144500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>174900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>182900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>174700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>148800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>144800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>171100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>140300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>118400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>134300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>152800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>146300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>217400</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>600</v>
       </c>
       <c r="R60" s="3">
         <v>600</v>
@@ -4057,11 +4197,11 @@
         <v>600</v>
       </c>
       <c r="T60" s="3">
+        <v>600</v>
+      </c>
+      <c r="U60" s="3">
         <v>100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4074,43 +4214,46 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="J61" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K61" s="3">
         <v>7100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7400</v>
-      </c>
-      <c r="N61" s="3">
-        <v>100</v>
       </c>
       <c r="O61" s="3">
         <v>100</v>
@@ -4119,7 +4262,7 @@
         <v>100</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -4145,52 +4288,55 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>19100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>20000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>19800</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G62" s="3">
-        <v>20000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>18700</v>
-      </c>
-      <c r="I62" s="3">
-        <v>19200</v>
-      </c>
-      <c r="J62" s="3">
+        <v>900</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>18300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>27000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>28000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>38400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>29900</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>9700</v>
       </c>
       <c r="R62" s="3">
         <v>9700</v>
@@ -4198,8 +4344,8 @@
       <c r="S62" s="3">
         <v>9700</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
+      <c r="T62" s="3">
+        <v>9700</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
@@ -4216,8 +4362,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4287,8 +4436,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4358,8 +4510,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4429,52 +4584,55 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>169600</v>
+      </c>
+      <c r="E66" s="3">
         <v>163600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>194900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>202700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>194800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>167500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>164000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>196500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>161100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>141200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>168700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>180900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>184800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>247400</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>10200</v>
       </c>
       <c r="R66" s="3">
         <v>10200</v>
@@ -4483,11 +4641,11 @@
         <v>10200</v>
       </c>
       <c r="T66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="U66" s="3">
         <v>100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4500,8 +4658,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4527,8 +4688,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4598,8 +4760,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4669,8 +4834,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4740,8 +4908,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4811,64 +4982,67 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1059300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1071800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1050000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1024500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-986000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-974400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-964100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-939000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-811200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-802300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-797500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-757300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-704000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-634100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-600</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-300</v>
       </c>
       <c r="S72" s="3">
         <v>-300</v>
       </c>
       <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
@@ -4882,8 +5056,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4953,8 +5130,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5024,8 +5204,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5095,64 +5278,67 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>555300</v>
+      </c>
+      <c r="E76" s="3">
         <v>552400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>550500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>573000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>577400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>601300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>593900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>576800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>572900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>636800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>691100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>706200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>712100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>642600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>267200</v>
-      </c>
-      <c r="R76" s="3">
-        <v>267500</v>
       </c>
       <c r="S76" s="3">
         <v>267500</v>
       </c>
       <c r="T76" s="3">
-        <v>0</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+        <v>267500</v>
+      </c>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
@@ -5166,8 +5352,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5237,70 +5426,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5313,64 +5505,67 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-38500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-127700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-40200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-64600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-70000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-464200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5300</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-300</v>
       </c>
       <c r="S81" s="3">
         <v>-300</v>
       </c>
       <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="U81" s="3">
+        <v>0</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
@@ -5384,8 +5579,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5411,64 +5609,65 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>20700</v>
+        <v>-900</v>
       </c>
       <c r="E83" s="3">
-        <v>21100</v>
+        <v>1300</v>
       </c>
       <c r="F83" s="3">
-        <v>24300</v>
+        <v>1200</v>
       </c>
       <c r="G83" s="3">
-        <v>18000</v>
+        <v>700</v>
       </c>
       <c r="H83" s="3">
-        <v>17700</v>
+        <v>-200</v>
       </c>
       <c r="I83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K83" s="3">
+        <v>17100</v>
+      </c>
+      <c r="L83" s="3">
+        <v>16700</v>
+      </c>
+      <c r="M83" s="3">
         <v>17300</v>
       </c>
-      <c r="J83" s="3">
-        <v>17100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>16700</v>
-      </c>
-      <c r="L83" s="3">
-        <v>17300</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>17500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>17400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>19500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5482,8 +5681,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5553,8 +5755,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5624,8 +5829,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5695,8 +5903,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5766,8 +5977,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5837,64 +6051,67 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E89" s="3">
         <v>13400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-18800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>23100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-25300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-34100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-29900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
@@ -5908,8 +6125,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5935,64 +6155,65 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-16100</v>
+        <v>-4900</v>
       </c>
       <c r="E91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="M91" s="3">
         <v>-12400</v>
       </c>
-      <c r="F91" s="3">
-        <v>-13400</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-12300</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-11200</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-12400</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -6006,8 +6227,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6077,8 +6301,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6148,58 +6375,61 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-35200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-80500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4200</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -6210,8 +6440,8 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -6219,8 +6449,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6246,31 +6479,32 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6317,8 +6551,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6388,8 +6625,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6459,8 +6699,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6530,8 +6773,11 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6539,11 +6785,11 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-7600</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -6551,11 +6797,11 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
@@ -6566,28 +6812,28 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>33400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>375700</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>277600</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
@@ -6601,64 +6847,67 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>2700</v>
+        <v>900</v>
       </c>
       <c r="E101" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="F101" s="3">
-        <v>-1200</v>
+        <v>800</v>
       </c>
       <c r="G101" s="3">
-        <v>900</v>
+        <v>18700</v>
       </c>
       <c r="H101" s="3">
-        <v>-400</v>
+        <v>-10400</v>
       </c>
       <c r="I101" s="3">
-        <v>800</v>
+        <v>-9800</v>
       </c>
       <c r="J101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K101" s="3">
         <v>18700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-10400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -6672,64 +6921,67 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-33000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-27500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-24600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-48200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-41100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>264800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1500</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
@@ -6741,6 +6993,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="92">
   <si>
     <t>GENI</t>
   </si>
@@ -656,101 +656,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -763,59 +763,62 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>175500</v>
+      </c>
+      <c r="E8" s="3">
         <v>120200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>95400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>119700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>127200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>101700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>86800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>97200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>105300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>78700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>71100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>85900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>84000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>69100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>55800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>53700</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -828,8 +831,8 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
@@ -837,59 +840,62 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E9" s="3">
         <v>80100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>67100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>106900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>116700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>77400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>62200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>87700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>102200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>72800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>61800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>101400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>109400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>86400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>240200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>40100</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -911,59 +917,62 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E10" s="3">
         <v>40100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>28400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-15500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-25400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-184400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13600</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -985,8 +994,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1013,59 +1025,60 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E12" s="3">
         <v>5800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3300</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,8 +1100,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1161,59 +1177,62 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>11900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1500</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1226,8 +1245,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1235,35 +1254,38 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E15" s="3">
         <v>8900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>30200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1309,8 +1331,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1334,67 +1359,68 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>183000</v>
+      </c>
+      <c r="E17" s="3">
         <v>125800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>114800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>143500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>161200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>109800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>94200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>119400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>150200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>112000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>110800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>150900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>160300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>133900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>485000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>56800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>300</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
+      <c r="V17" s="3">
+        <v>0</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
@@ -1408,59 +1434,62 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-19400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-23800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-34100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-22200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-44900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-33300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-39700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-65000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-76300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-64800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-429200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,8 +1511,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1510,59 +1542,60 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-23200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-81500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>25000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>35300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>25800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>11700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-34600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2500</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,59 +1617,62 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E21" s="3">
         <v>26400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-15600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>18800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-109200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-21700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-47200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-50900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-451500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,16 +1694,19 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
+        <v>1300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
@@ -1675,17 +1714,17 @@
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="H22" s="3">
+        <v>400</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>400</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>400</v>
@@ -1696,11 +1735,11 @@
       <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3">
+        <v>400</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1732,67 +1771,70 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="E23" s="3">
         <v>17100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-24400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-38900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-126700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-39600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-64600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-70500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-463800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5600</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-300</v>
       </c>
       <c r="T23" s="3">
         <v>-300</v>
       </c>
       <c r="U23" s="3">
-        <v>0</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="V23" s="3">
+        <v>0</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
@@ -1806,64 +1848,67 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E24" s="3">
         <v>4600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-11300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-300</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
@@ -1871,8 +1916,8 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -1880,8 +1925,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1954,67 +2002,70 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E26" s="3">
         <v>12500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-21800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-38500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-127700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-40200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-53300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-70000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-464200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5300</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-300</v>
       </c>
       <c r="T26" s="3">
         <v>-300</v>
       </c>
       <c r="U26" s="3">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="V26" s="3">
+        <v>0</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
@@ -2028,67 +2079,70 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E27" s="3">
         <v>12500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-21800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-38500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-127700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-40200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-64600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-70000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-464200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5300</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-300</v>
       </c>
       <c r="T27" s="3">
         <v>-300</v>
       </c>
       <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="V27" s="3">
+        <v>0</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
@@ -2102,8 +2156,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2176,8 +2233,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2250,8 +2310,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2324,8 +2387,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2398,59 +2464,62 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="E32" s="3">
         <v>23200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>81500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-25000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-35300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-25800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-11700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>34600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2500</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2472,67 +2541,70 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E33" s="3">
         <v>12500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-21800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-38500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-127700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-40200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-64600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-70000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-464200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5300</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-300</v>
       </c>
       <c r="T33" s="3">
         <v>-300</v>
       </c>
       <c r="U33" s="3">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="V33" s="3">
+        <v>0</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
@@ -2546,8 +2618,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2620,67 +2695,70 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E35" s="3">
         <v>12500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-21800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-38500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-127700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-40200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-64600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-70000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-464200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5300</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-300</v>
       </c>
       <c r="T35" s="3">
         <v>-300</v>
       </c>
       <c r="U35" s="3">
-        <v>0</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="V35" s="3">
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
@@ -2694,73 +2772,76 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2854,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2801,8 +2885,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2829,67 +2914,68 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>110200</v>
+      </c>
+      <c r="E41" s="3">
         <v>42300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>67700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>67500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>100300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>92000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>89800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>94400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>122700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>116900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>138500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>174200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>222400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>234200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>275300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1000</v>
-      </c>
-      <c r="S41" s="3">
-        <v>1500</v>
       </c>
       <c r="T41" s="3">
         <v>1500</v>
       </c>
       <c r="U41" s="3">
-        <v>0</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="V41" s="3">
+        <v>0</v>
       </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
@@ -2903,8 +2989,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2912,13 +3001,13 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>5800</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -2977,56 +3066,59 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>124400</v>
+      </c>
+      <c r="E43" s="3">
         <v>128800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>98400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>131900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>116900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>105600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>99300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>82400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>73200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>69200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>56900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>89600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>77300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>66000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>57800</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3042,8 +3134,8 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3051,8 +3143,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3063,49 +3158,49 @@
         <v>500</v>
       </c>
       <c r="F44" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G44" s="3">
         <v>300</v>
       </c>
       <c r="H44" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I44" s="3">
         <v>400</v>
       </c>
       <c r="J44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K44" s="3">
         <v>300</v>
       </c>
       <c r="L44" s="3">
+        <v>300</v>
+      </c>
+      <c r="M44" s="3">
         <v>400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>300</v>
-      </c>
-      <c r="N44" s="3">
-        <v>500</v>
       </c>
       <c r="O44" s="3">
         <v>500</v>
       </c>
       <c r="P44" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q44" s="3">
         <v>600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>400</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
@@ -3125,13 +3220,16 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>1100</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -3151,38 +3249,38 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>40300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>51700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>37800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>29700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>24400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>33100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
-      </c>
-      <c r="S45" s="3">
-        <v>200</v>
       </c>
       <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
+      <c r="U45" s="3">
+        <v>200</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
@@ -3199,67 +3297,70 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>288600</v>
+      </c>
+      <c r="E46" s="3">
         <v>224400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>222500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>229200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>244800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>248100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>222200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>218400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>236500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>238100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>233500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>294000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>324700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>333900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>344600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1400</v>
-      </c>
-      <c r="S46" s="3">
-        <v>1700</v>
       </c>
       <c r="T46" s="3">
         <v>1700</v>
       </c>
       <c r="U46" s="3">
-        <v>0</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
+        <v>1700</v>
+      </c>
+      <c r="V46" s="3">
+        <v>0</v>
       </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
@@ -3273,64 +3374,67 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E47" s="3">
         <v>30700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>28900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>25000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>26400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>24700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>24000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>23000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>32800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>29400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>29300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>31100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>276100</v>
-      </c>
-      <c r="S47" s="3">
-        <v>276000</v>
       </c>
       <c r="T47" s="3">
         <v>276000</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>276000</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3347,56 +3451,59 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E48" s="3">
         <v>24900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>18600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>17700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>19300</v>
       </c>
       <c r="K48" s="3">
         <v>19300</v>
       </c>
       <c r="L48" s="3">
+        <v>19300</v>
+      </c>
+      <c r="M48" s="3">
         <v>11800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10400</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3412,8 +3519,8 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -3421,56 +3528,59 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>441600</v>
+      </c>
+      <c r="E49" s="3">
         <v>441100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>440500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>443100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>455700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>447200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>469500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>462000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>459100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>428900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>473600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>516700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>537600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>542500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>523100</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3486,8 +3596,8 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -3495,8 +3605,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3569,8 +3682,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3643,8 +3759,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3652,59 +3771,59 @@
         <v>1600</v>
       </c>
       <c r="E52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F52" s="3">
         <v>1500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>28300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>33500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>33400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>28000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12000</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,8 +3836,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3791,68 +3913,71 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>792300</v>
+      </c>
+      <c r="E54" s="3">
         <v>724900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>716000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>745400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>775700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>772200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>768800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>757900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>773300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>734000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>778000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>859700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>887100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>896900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>890000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>277400</v>
-      </c>
-      <c r="S54" s="3">
-        <v>277800</v>
       </c>
       <c r="T54" s="3">
         <v>277800</v>
       </c>
       <c r="U54" s="3">
+        <v>277800</v>
+      </c>
+      <c r="V54" s="3">
         <v>200</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3990,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3893,8 +4021,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3921,55 +4050,56 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E57" s="3">
         <v>26400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>39500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>51400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>57400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>43700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>33100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>30600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>20700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11800</v>
-      </c>
-      <c r="R57" s="3">
-        <v>200</v>
       </c>
       <c r="S57" s="3">
         <v>200</v>
@@ -3978,10 +4108,10 @@
         <v>200</v>
       </c>
       <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="V57" s="3">
+        <v>0</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
@@ -3995,55 +4125,58 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="E58" s="3">
         <v>3300</v>
       </c>
       <c r="F58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G58" s="3">
         <v>3500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10700</v>
-      </c>
-      <c r="I58" s="3">
-        <v>10500</v>
       </c>
       <c r="J58" s="3">
         <v>10500</v>
       </c>
       <c r="K58" s="3">
+        <v>10500</v>
+      </c>
+      <c r="L58" s="3">
         <v>7400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7700</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -4051,12 +4184,12 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3">
         <v>100</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4069,68 +4202,71 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E59" s="3">
         <v>51600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>50300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>56600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>58000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>54300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>55000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>52700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>130600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>102500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>98100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>105800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>132900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>135000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>205700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>400</v>
-      </c>
-      <c r="S59" s="3">
-        <v>300</v>
       </c>
       <c r="T59" s="3">
         <v>300</v>
       </c>
       <c r="U59" s="3">
+        <v>300</v>
+      </c>
+      <c r="V59" s="3">
         <v>100</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4143,55 +4279,58 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>201600</v>
+      </c>
+      <c r="E60" s="3">
         <v>149100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>144500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>174900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>182900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>174700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>148800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>144800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>171100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>140300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>118400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>134300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>152800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>146300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>217400</v>
-      </c>
-      <c r="R60" s="3">
-        <v>600</v>
       </c>
       <c r="S60" s="3">
         <v>600</v>
@@ -4200,11 +4339,11 @@
         <v>600</v>
       </c>
       <c r="U60" s="3">
+        <v>600</v>
+      </c>
+      <c r="V60" s="3">
         <v>100</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,46 +4356,49 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E61" s="3">
         <v>4900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7400</v>
-      </c>
-      <c r="O61" s="3">
-        <v>100</v>
       </c>
       <c r="P61" s="3">
         <v>100</v>
@@ -4265,7 +4407,7 @@
         <v>100</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -4291,8 +4433,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4305,41 +4450,41 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
         <v>900</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>18300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>27000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>28000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>38400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>29900</v>
-      </c>
-      <c r="R62" s="3">
-        <v>9700</v>
       </c>
       <c r="S62" s="3">
         <v>9700</v>
@@ -4347,8 +4492,8 @@
       <c r="T62" s="3">
         <v>9700</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
+      <c r="U62" s="3">
+        <v>9700</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
@@ -4365,8 +4510,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4439,8 +4587,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4513,8 +4664,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4587,55 +4741,58 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>219900</v>
+      </c>
+      <c r="E66" s="3">
         <v>169600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>163600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>194900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>202700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>194800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>167500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>164000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>196500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>161100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>141200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>168700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>180900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>184800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>247400</v>
-      </c>
-      <c r="R66" s="3">
-        <v>10200</v>
       </c>
       <c r="S66" s="3">
         <v>10200</v>
@@ -4644,11 +4801,11 @@
         <v>10200</v>
       </c>
       <c r="U66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="V66" s="3">
         <v>100</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4661,8 +4818,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4689,8 +4849,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4763,8 +4924,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4837,8 +5001,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4911,8 +5078,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4985,67 +5155,70 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1087500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1059300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1071800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1050000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1024500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-986000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-974400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-964100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-939000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-811200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-802300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-797500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-757300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-704000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-634100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-600</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-300</v>
       </c>
       <c r="T72" s="3">
         <v>-300</v>
       </c>
       <c r="U72" s="3">
-        <v>0</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="V72" s="3">
+        <v>0</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
@@ -5059,8 +5232,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5133,8 +5309,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5207,8 +5386,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5281,67 +5463,70 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>572400</v>
+      </c>
+      <c r="E76" s="3">
         <v>555300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>552400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>550500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>573000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>577400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>601300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>593900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>576800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>572900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>636800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>691100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>706200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>712100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>642600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>267200</v>
-      </c>
-      <c r="S76" s="3">
-        <v>267500</v>
       </c>
       <c r="T76" s="3">
         <v>267500</v>
       </c>
       <c r="U76" s="3">
-        <v>0</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
+        <v>267500</v>
+      </c>
+      <c r="V76" s="3">
+        <v>0</v>
       </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
@@ -5355,8 +5540,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5429,73 +5617,76 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5508,67 +5699,70 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E81" s="3">
         <v>12500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-21800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-38500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-127700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-40200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-64600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-70000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-464200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5300</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-300</v>
       </c>
       <c r="T81" s="3">
         <v>-300</v>
       </c>
       <c r="U81" s="3">
-        <v>0</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="V81" s="3">
+        <v>0</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
@@ -5582,8 +5776,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5610,67 +5807,68 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E83" s="3">
         <v>-900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>17100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>16700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>17300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>17500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>17400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>19500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>10100</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -5684,8 +5882,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5758,8 +5959,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5832,8 +6036,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5906,8 +6113,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5980,8 +6190,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6054,67 +6267,70 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-18800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>23100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-25300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-34100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-29900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
@@ -6128,8 +6344,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6156,67 +6375,68 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -6230,8 +6450,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6304,8 +6527,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6378,61 +6604,64 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-35200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-80500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4200</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -6443,8 +6672,8 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -6452,8 +6681,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6480,8 +6712,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6506,8 +6739,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6554,8 +6787,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6628,8 +6864,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6702,8 +6941,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6776,8 +7018,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6788,11 +7033,11 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-7600</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -6800,11 +7045,11 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-600</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -6815,28 +7060,28 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>1300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>33400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>375700</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>277600</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
@@ -6850,67 +7095,70 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>18700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-10400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>18700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-10400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -6924,67 +7172,70 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-23900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-33000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-16300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-27500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-24600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-48200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-41100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>264800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1500</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
@@ -6996,6 +7247,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
   <si>
     <t>GENI</t>
   </si>
@@ -656,104 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -766,62 +767,65 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E8" s="3">
         <v>175500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>120200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>95400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>119700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>127200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>101700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>86800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>97200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>105300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>78700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>71100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>85900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>84000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>69100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>55800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>53700</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -834,8 +838,8 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
@@ -843,62 +847,65 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>108700</v>
+      </c>
+      <c r="E9" s="3">
         <v>128100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>80100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>67100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>106900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>116700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>77400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>62200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>87700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>102200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>72800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>61800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>101400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>109400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>86400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>240200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>40100</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -920,62 +927,65 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E10" s="3">
         <v>47400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>40100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>28400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-15500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-25400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-17300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-184400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>13600</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -997,8 +1007,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1026,62 +1039,63 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E12" s="3">
         <v>4900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>9800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3300</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1103,8 +1117,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1180,62 +1197,65 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>11900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1500</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>700</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1248,8 +1268,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1257,8 +1277,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1266,29 +1289,29 @@
         <v>4100</v>
       </c>
       <c r="E15" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F15" s="3">
         <v>8900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>30200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1334,8 +1357,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1360,70 +1386,71 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>163700</v>
+      </c>
+      <c r="E17" s="3">
         <v>183000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>125800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>114800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>143500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>161200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>109800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>94200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>119400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>150200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>112000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>110800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>150900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>160300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>133900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>485000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>56800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>300</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
+      <c r="W17" s="3">
+        <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
@@ -1437,62 +1464,65 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-19400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-23800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-34100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-22200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-44900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-33300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-39700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-65000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-76300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-64800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-429200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1514,8 +1544,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1543,62 +1576,63 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E20" s="3">
         <v>25700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-23200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-81500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>25000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>35300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>25800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>11700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-34600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2500</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1620,62 +1654,65 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-29100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>26400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-13000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-15600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>18800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-109200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-21700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-47200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-50900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-451500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4600</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1697,37 +1734,40 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>1300</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
-        <v>400</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>400</v>
@@ -1738,11 +1778,11 @@
       <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1774,70 +1814,73 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-32100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>17100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-38900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-126700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-39600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-64600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-70500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-463800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5600</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-300</v>
       </c>
       <c r="U23" s="3">
         <v>-300</v>
       </c>
       <c r="V23" s="3">
-        <v>0</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="W23" s="3">
+        <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
@@ -1851,67 +1894,70 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-300</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
@@ -1919,8 +1965,8 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -1928,8 +1974,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2005,70 +2054,73 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-28200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-21800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-25500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-38500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-127700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-40200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-53300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-70000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-464200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5300</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-300</v>
       </c>
       <c r="U26" s="3">
         <v>-300</v>
       </c>
       <c r="V26" s="3">
-        <v>0</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="W26" s="3">
+        <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
@@ -2082,70 +2134,73 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-25500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-38500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-127700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-40200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-64600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-70000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-464200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5300</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-300</v>
       </c>
       <c r="U27" s="3">
         <v>-300</v>
       </c>
       <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="W27" s="3">
+        <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
@@ -2159,8 +2214,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2236,8 +2294,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2313,8 +2374,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2390,8 +2454,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2467,62 +2534,65 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-25700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>23200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>81500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-25000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-35300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-25800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>34600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2500</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2544,70 +2614,73 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-28200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-21800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-25500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-38500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-127700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-40200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-64600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-70000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-464200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5300</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-300</v>
       </c>
       <c r="U33" s="3">
         <v>-300</v>
       </c>
       <c r="V33" s="3">
-        <v>0</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="W33" s="3">
+        <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
@@ -2621,8 +2694,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2698,70 +2774,73 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-28200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-21800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-25500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-38500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-127700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-40200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-64600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-70000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-464200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5300</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-300</v>
       </c>
       <c r="U35" s="3">
         <v>-300</v>
       </c>
       <c r="V35" s="3">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="W35" s="3">
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
@@ -2775,76 +2854,79 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2857,8 +2939,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2886,8 +2971,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2915,70 +3001,71 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>209800</v>
+      </c>
+      <c r="E41" s="3">
         <v>110200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>42300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>67700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>67500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>100300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>92000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>89800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>94400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>122700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>116900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>138500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>174200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>222400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>234200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>275300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1000</v>
-      </c>
-      <c r="T41" s="3">
-        <v>1500</v>
       </c>
       <c r="U41" s="3">
         <v>1500</v>
       </c>
       <c r="V41" s="3">
-        <v>0</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="W41" s="3">
+        <v>0</v>
       </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
@@ -2992,8 +3079,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3004,13 +3094,13 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>5800</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -3069,59 +3159,62 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E43" s="3">
         <v>124400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>128800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>98400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>131900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>116900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>105600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>99300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>82400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>73200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>69200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>56900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>89600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>77300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>66000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>57800</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3137,8 +3230,8 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -3146,13 +3239,16 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E44" s="3">
         <v>500</v>
@@ -3161,49 +3257,49 @@
         <v>500</v>
       </c>
       <c r="G44" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H44" s="3">
         <v>300</v>
       </c>
       <c r="I44" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J44" s="3">
         <v>400</v>
       </c>
       <c r="K44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L44" s="3">
         <v>300</v>
       </c>
       <c r="M44" s="3">
+        <v>300</v>
+      </c>
+      <c r="N44" s="3">
         <v>400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>300</v>
-      </c>
-      <c r="O44" s="3">
-        <v>500</v>
       </c>
       <c r="P44" s="3">
         <v>500</v>
       </c>
       <c r="Q44" s="3">
+        <v>500</v>
+      </c>
+      <c r="R44" s="3">
         <v>600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>400</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -3223,17 +3319,20 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1100</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3252,38 +3351,38 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>40300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>51700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>37800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>29700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>24400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>33100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
-      </c>
-      <c r="T45" s="3">
-        <v>200</v>
       </c>
       <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
+      <c r="V45" s="3">
+        <v>200</v>
       </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
@@ -3300,70 +3399,73 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>396600</v>
+      </c>
+      <c r="E46" s="3">
         <v>288600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>224400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>222500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>229200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>244800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>248100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>222200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>218400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>236500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>238100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>233500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>294000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>324700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>333900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>344600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1400</v>
-      </c>
-      <c r="T46" s="3">
-        <v>1700</v>
       </c>
       <c r="U46" s="3">
         <v>1700</v>
       </c>
       <c r="V46" s="3">
-        <v>0</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
+        <v>1700</v>
+      </c>
+      <c r="W46" s="3">
+        <v>0</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
@@ -3377,67 +3479,70 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E47" s="3">
         <v>31700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>30700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>25000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>26400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>24700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>24000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>23000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>32800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>29400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>29300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>31100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3">
         <v>276100</v>
-      </c>
-      <c r="T47" s="3">
-        <v>276000</v>
       </c>
       <c r="U47" s="3">
         <v>276000</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
+      <c r="V47" s="3">
+        <v>276000</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
@@ -3454,59 +3559,62 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E48" s="3">
         <v>26500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>18600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17700</v>
-      </c>
-      <c r="K48" s="3">
-        <v>19300</v>
       </c>
       <c r="L48" s="3">
         <v>19300</v>
       </c>
       <c r="M48" s="3">
+        <v>19300</v>
+      </c>
+      <c r="N48" s="3">
         <v>11800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10400</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3522,8 +3630,8 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
@@ -3531,59 +3639,62 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>441300</v>
+      </c>
+      <c r="E49" s="3">
         <v>441600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>441100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>440500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>443100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>455700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>447200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>469500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>462000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>459100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>428900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>473600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>516700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>537600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>542500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>523100</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3599,8 +3710,8 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -3608,8 +3719,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3685,8 +3799,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3762,71 +3879,74 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="E52" s="3">
         <v>1600</v>
       </c>
       <c r="F52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G52" s="3">
         <v>1500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>28300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>33500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>33400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3839,8 +3959,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3916,71 +4039,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>906700</v>
+      </c>
+      <c r="E54" s="3">
         <v>792300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>724900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>716000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>745400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>775700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>772200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>768800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>757900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>773300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>734000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>778000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>859700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>887100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>896900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>890000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>277400</v>
-      </c>
-      <c r="T54" s="3">
-        <v>277800</v>
       </c>
       <c r="U54" s="3">
         <v>277800</v>
       </c>
       <c r="V54" s="3">
+        <v>277800</v>
+      </c>
+      <c r="W54" s="3">
         <v>200</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3993,8 +4119,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4022,8 +4151,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4051,58 +4181,59 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E57" s="3">
         <v>36700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>26400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>39500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>51400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>57400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>23600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>21400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>33100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>30600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>19900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11800</v>
-      </c>
-      <c r="S57" s="3">
-        <v>200</v>
       </c>
       <c r="T57" s="3">
         <v>200</v>
@@ -4111,10 +4242,10 @@
         <v>200</v>
       </c>
       <c r="V57" s="3">
-        <v>0</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
@@ -4128,8 +4259,11 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4137,49 +4271,49 @@
         <v>3000</v>
       </c>
       <c r="E58" s="3">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="F58" s="3">
         <v>3300</v>
       </c>
       <c r="G58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H58" s="3">
         <v>3500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10700</v>
-      </c>
-      <c r="J58" s="3">
-        <v>10500</v>
       </c>
       <c r="K58" s="3">
         <v>10500</v>
       </c>
       <c r="L58" s="3">
+        <v>10500</v>
+      </c>
+      <c r="M58" s="3">
         <v>7400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7700</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -4187,12 +4321,12 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
         <v>100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4205,71 +4339,74 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E59" s="3">
         <v>82000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>51600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>50300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>56600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>58000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>54300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>55000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>52700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>130600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>102500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>98100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>105800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>132900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>135000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>205700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>400</v>
-      </c>
-      <c r="T59" s="3">
-        <v>300</v>
       </c>
       <c r="U59" s="3">
         <v>300</v>
       </c>
       <c r="V59" s="3">
+        <v>300</v>
+      </c>
+      <c r="W59" s="3">
         <v>100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,58 +4419,61 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>170700</v>
+      </c>
+      <c r="E60" s="3">
         <v>201600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>149100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>144500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>174900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>182900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>174700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>148800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>144800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>171100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>140300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>118400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>134300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>152800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>146300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>217400</v>
-      </c>
-      <c r="S60" s="3">
-        <v>600</v>
       </c>
       <c r="T60" s="3">
         <v>600</v>
@@ -4342,11 +4482,11 @@
         <v>600</v>
       </c>
       <c r="V60" s="3">
+        <v>600</v>
+      </c>
+      <c r="W60" s="3">
         <v>100</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4359,49 +4499,52 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E61" s="3">
         <v>4500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7400</v>
-      </c>
-      <c r="P61" s="3">
-        <v>100</v>
       </c>
       <c r="Q61" s="3">
         <v>100</v>
@@ -4410,7 +4553,7 @@
         <v>100</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -4436,8 +4579,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4453,41 +4599,41 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
         <v>900</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>18300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>27000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>28000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>38400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>29900</v>
-      </c>
-      <c r="S62" s="3">
-        <v>9700</v>
       </c>
       <c r="T62" s="3">
         <v>9700</v>
@@ -4495,8 +4641,8 @@
       <c r="U62" s="3">
         <v>9700</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
+      <c r="V62" s="3">
+        <v>9700</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
@@ -4513,8 +4659,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4590,8 +4739,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4667,8 +4819,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4744,58 +4899,61 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>195800</v>
+      </c>
+      <c r="E66" s="3">
         <v>219900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>169600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>163600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>194900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>202700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>194800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>167500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>164000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>196500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>161100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>141200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>168700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>180900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>184800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>247400</v>
-      </c>
-      <c r="S66" s="3">
-        <v>10200</v>
       </c>
       <c r="T66" s="3">
         <v>10200</v>
@@ -4804,11 +4962,11 @@
         <v>10200</v>
       </c>
       <c r="V66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="W66" s="3">
         <v>100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4821,8 +4979,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4850,8 +5011,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4927,8 +5089,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5004,8 +5169,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5081,8 +5249,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5158,70 +5329,73 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1095700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1087500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1059300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1071800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1050000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1024500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-986000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-974400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-964100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-939000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-811200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-802300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-797500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-757300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-704000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-634100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-600</v>
-      </c>
-      <c r="T72" s="3">
-        <v>-300</v>
       </c>
       <c r="U72" s="3">
         <v>-300</v>
       </c>
       <c r="V72" s="3">
-        <v>0</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="W72" s="3">
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
@@ -5235,8 +5409,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5312,8 +5489,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5389,8 +5569,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5466,70 +5649,73 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>710800</v>
+      </c>
+      <c r="E76" s="3">
         <v>572400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>555300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>552400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>550500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>573000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>577400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>601300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>593900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>576800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>572900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>636800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>691100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>706200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>712100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>642600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>267200</v>
-      </c>
-      <c r="T76" s="3">
-        <v>267500</v>
       </c>
       <c r="U76" s="3">
         <v>267500</v>
       </c>
       <c r="V76" s="3">
-        <v>0</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
+        <v>267500</v>
+      </c>
+      <c r="W76" s="3">
+        <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
@@ -5543,8 +5729,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5620,76 +5809,79 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5702,70 +5894,73 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-28200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-21800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-25500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-38500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-127700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-40200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-64600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-70000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-464200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5300</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-300</v>
       </c>
       <c r="U81" s="3">
         <v>-300</v>
       </c>
       <c r="V81" s="3">
-        <v>0</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="W81" s="3">
+        <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
@@ -5779,8 +5974,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5808,70 +6006,71 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>17100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>16700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>17300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>17500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>17400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>19500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>10100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -5885,8 +6084,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5962,8 +6164,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6039,8 +6244,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6116,8 +6324,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6193,8 +6404,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6270,70 +6484,73 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E89" s="3">
         <v>86600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-14600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>24000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-18800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>23100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-25300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-34100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-29900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-100</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
+      <c r="W89" s="3">
+        <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
@@ -6347,8 +6564,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6376,70 +6596,71 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -6453,8 +6674,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6530,8 +6754,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6607,64 +6834,67 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-16700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-35200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-80500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4200</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
@@ -6675,8 +6905,8 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -6684,8 +6914,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6713,8 +6946,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6742,8 +6976,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6790,8 +7024,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6867,8 +7104,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6944,8 +7184,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7021,13 +7264,16 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>144000</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -7036,11 +7282,11 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-7600</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -7048,11 +7294,11 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-600</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -7063,28 +7309,28 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>33400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>375700</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>277600</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
+      <c r="W100" s="3">
+        <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
@@ -7098,70 +7344,73 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>18700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-10400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>18700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-10400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -7175,70 +7424,73 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100400</v>
+      </c>
+      <c r="E102" s="3">
         <v>66200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-23900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-33000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-16300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-27500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-24600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-48200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-41100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>264800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1500</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
+      <c r="W102" s="3">
+        <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
@@ -7250,6 +7502,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="92">
   <si>
     <t>GENI</t>
   </si>
@@ -656,108 +656,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -770,65 +771,68 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>118700</v>
+      </c>
+      <c r="E8" s="3">
         <v>144000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>175500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>120200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>95400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>119700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>127200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>101700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>86800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>97200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>105300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>78700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>71100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>85900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>84000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>69100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>55800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>53700</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -841,8 +845,8 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
@@ -850,65 +854,68 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>109800</v>
+      </c>
+      <c r="E9" s="3">
         <v>108700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>128100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>80100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>67100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>106900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>116700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>77400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>62200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>87700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>102200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>72800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>61800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>101400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>109400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>86400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>240200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>40100</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -930,65 +937,68 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E10" s="3">
         <v>35300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>47400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>40100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>28400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>12900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-15500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-25400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-17300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-184400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>13600</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1010,8 +1020,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1040,65 +1053,66 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E12" s="3">
         <v>8100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5800</v>
       </c>
-      <c r="G12" s="3">
-        <v>7200</v>
-      </c>
       <c r="H12" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I12" s="3">
         <v>6300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3300</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1120,8 +1134,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1200,65 +1217,68 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G14" s="3">
+        <v>400</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J14" s="3">
+        <v>11900</v>
+      </c>
+      <c r="K14" s="3">
+        <v>800</v>
+      </c>
+      <c r="L14" s="3">
+        <v>900</v>
+      </c>
+      <c r="M14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>100</v>
+      </c>
+      <c r="R14" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="T14" s="3">
+        <v>6100</v>
+      </c>
+      <c r="U14" s="3">
         <v>700</v>
       </c>
-      <c r="E14" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="F14" s="3">
-        <v>400</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H14" s="3">
-        <v>500</v>
-      </c>
-      <c r="I14" s="3">
-        <v>11900</v>
-      </c>
-      <c r="J14" s="3">
-        <v>800</v>
-      </c>
-      <c r="K14" s="3">
-        <v>900</v>
-      </c>
-      <c r="L14" s="3">
-        <v>3300</v>
-      </c>
-      <c r="M14" s="3">
-        <v>1500</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>3200</v>
-      </c>
-      <c r="R14" s="3">
-        <v>2900</v>
-      </c>
-      <c r="S14" s="3">
-        <v>6100</v>
-      </c>
-      <c r="T14" s="3">
-        <v>700</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1271,8 +1291,8 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1280,41 +1300,44 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>4100</v>
+        <v>27600</v>
       </c>
       <c r="E15" s="3">
         <v>4100</v>
       </c>
       <c r="F15" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G15" s="3">
         <v>8900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>30200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>24000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1360,8 +1383,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1387,73 +1413,74 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>163700</v>
+        <v>186800</v>
       </c>
       <c r="E17" s="3">
+        <v>160300</v>
+      </c>
+      <c r="F17" s="3">
         <v>183000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>125800</v>
       </c>
-      <c r="G17" s="3">
-        <v>114800</v>
-      </c>
       <c r="H17" s="3">
-        <v>143500</v>
+        <v>113700</v>
       </c>
       <c r="I17" s="3">
+        <v>142300</v>
+      </c>
+      <c r="J17" s="3">
         <v>161200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>109800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>94200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>119400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>150200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>112000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>110800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>150900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>160300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>133900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>485000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>56800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>300</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
+      <c r="X17" s="3">
+        <v>0</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
@@ -1467,65 +1494,68 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-19700</v>
+        <v>-68100</v>
       </c>
       <c r="E18" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5600</v>
       </c>
-      <c r="G18" s="3">
-        <v>-19400</v>
-      </c>
       <c r="H18" s="3">
-        <v>-23800</v>
+        <v>-18200</v>
       </c>
       <c r="I18" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="J18" s="3">
         <v>-34100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-22200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-44900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-33300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-39700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-65000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-76300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-64800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-429200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,8 +1577,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1577,65 +1610,66 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-12300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>25700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-23200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-81500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>25000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>35300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>25800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>11700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-34600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2500</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1657,65 +1691,68 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3300</v>
+        <v>-12600</v>
       </c>
       <c r="E21" s="3">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-29100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26400</v>
       </c>
-      <c r="G21" s="3">
-        <v>8400</v>
-      </c>
       <c r="H21" s="3">
-        <v>-13000</v>
+        <v>9600</v>
       </c>
       <c r="I21" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="J21" s="3">
         <v>-15600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>18800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-109200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-47200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-50900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-451500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4600</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,40 +1774,43 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
         <v>1300</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>400</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3">
-        <v>400</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>400</v>
@@ -1781,11 +1821,11 @@
       <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3">
+        <v>400</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1817,73 +1857,76 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-52200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-32100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-23100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-38900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-126700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-39600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-64600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-70500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-463800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5600</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-300</v>
       </c>
       <c r="V23" s="3">
         <v>-300</v>
       </c>
       <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="X23" s="3">
+        <v>0</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
@@ -1897,70 +1940,73 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-11300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-300</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
@@ -1968,8 +2014,8 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
@@ -1977,8 +2023,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2057,73 +2106,76 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-21800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-11600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-127700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-53300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-70000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-464200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5300</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-300</v>
       </c>
       <c r="V26" s="3">
         <v>-300</v>
       </c>
       <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="X26" s="3">
+        <v>0</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
@@ -2137,73 +2189,76 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-21800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-11600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-127700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-64600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-70000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-464200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5300</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-300</v>
       </c>
       <c r="V27" s="3">
         <v>-300</v>
       </c>
       <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="X27" s="3">
+        <v>0</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
@@ -2217,8 +2272,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2297,8 +2355,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2377,8 +2438,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2457,8 +2521,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2537,65 +2604,68 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E32" s="3">
         <v>12300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-25700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>23200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>81500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-25000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-35300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-11700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>34600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2500</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2617,73 +2687,76 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-21800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-127700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-64600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-70000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-464200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5300</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-300</v>
       </c>
       <c r="V33" s="3">
         <v>-300</v>
       </c>
       <c r="W33" s="3">
-        <v>0</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="X33" s="3">
+        <v>0</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
@@ -2697,8 +2770,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2777,73 +2853,76 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-21800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-127700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-64600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-70000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-464200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5300</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-300</v>
       </c>
       <c r="V35" s="3">
         <v>-300</v>
       </c>
       <c r="W35" s="3">
-        <v>0</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="X35" s="3">
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
@@ -2857,79 +2936,82 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2942,8 +3024,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2972,8 +3057,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3002,73 +3088,74 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>221600</v>
+      </c>
+      <c r="E41" s="3">
         <v>209800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>110200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>42300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>67700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>67500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>92000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>89800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>94400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>122700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>116900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>138500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>174200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>222400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>234200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>275300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1000</v>
-      </c>
-      <c r="U41" s="3">
-        <v>1500</v>
       </c>
       <c r="V41" s="3">
         <v>1500</v>
       </c>
       <c r="W41" s="3">
-        <v>0</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="X41" s="3">
+        <v>0</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
@@ -3082,8 +3169,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3097,13 +3187,13 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>5800</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -3162,62 +3252,65 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>135300</v>
+      </c>
+      <c r="E43" s="3">
         <v>122000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>124400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>128800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>98400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>131900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>116900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>105600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>99300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>82400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>73200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>69200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>56900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>89600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>77300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>66000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>57800</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3233,8 +3326,8 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -3242,8 +3335,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3251,7 +3347,7 @@
         <v>400</v>
       </c>
       <c r="E44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F44" s="3">
         <v>500</v>
@@ -3260,49 +3356,49 @@
         <v>500</v>
       </c>
       <c r="H44" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I44" s="3">
         <v>300</v>
       </c>
       <c r="J44" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K44" s="3">
         <v>400</v>
       </c>
       <c r="L44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M44" s="3">
         <v>300</v>
       </c>
       <c r="N44" s="3">
+        <v>300</v>
+      </c>
+      <c r="O44" s="3">
         <v>400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>300</v>
-      </c>
-      <c r="P44" s="3">
-        <v>500</v>
       </c>
       <c r="Q44" s="3">
         <v>500</v>
       </c>
       <c r="R44" s="3">
+        <v>500</v>
+      </c>
+      <c r="S44" s="3">
         <v>600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>400</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -3322,8 +3418,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3331,11 +3430,11 @@
         <v>1200</v>
       </c>
       <c r="E45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F45" s="3">
         <v>1100</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3354,38 +3453,38 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>40300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>51700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>37800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>29700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>24400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>33100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>400</v>
-      </c>
-      <c r="U45" s="3">
-        <v>200</v>
       </c>
       <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
+      <c r="W45" s="3">
+        <v>200</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
@@ -3402,73 +3501,76 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>395700</v>
+      </c>
+      <c r="E46" s="3">
         <v>396600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>288600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>224400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>222500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>229200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>244800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>248100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>222200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>218400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>236500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>238100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>233500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>294000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>324700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>333900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>344600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1400</v>
-      </c>
-      <c r="U46" s="3">
-        <v>1700</v>
       </c>
       <c r="V46" s="3">
         <v>1700</v>
       </c>
       <c r="W46" s="3">
-        <v>0</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
+        <v>1700</v>
+      </c>
+      <c r="X46" s="3">
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
@@ -3482,70 +3584,73 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E47" s="3">
         <v>29300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>31700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>30700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>28900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>25000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>26400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>24700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>24000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>23000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>32800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>29400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>29300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>31100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3">
         <v>276100</v>
-      </c>
-      <c r="U47" s="3">
-        <v>276000</v>
       </c>
       <c r="V47" s="3">
         <v>276000</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
+      <c r="W47" s="3">
+        <v>276000</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
@@ -3562,62 +3667,65 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E48" s="3">
         <v>34600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>18600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17700</v>
-      </c>
-      <c r="L48" s="3">
-        <v>19300</v>
       </c>
       <c r="M48" s="3">
         <v>19300</v>
       </c>
       <c r="N48" s="3">
+        <v>19300</v>
+      </c>
+      <c r="O48" s="3">
         <v>11800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10400</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3633,8 +3741,8 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
@@ -3642,62 +3750,65 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>442300</v>
+      </c>
+      <c r="E49" s="3">
         <v>441300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>441600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>441100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>440500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>443100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>455700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>447200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>469500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>462000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>459100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>428900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>473600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>516700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>537600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>542500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>523100</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3713,8 +3824,8 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -3722,8 +3833,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3802,8 +3916,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3882,74 +3999,77 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E52" s="3">
         <v>2300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1600</v>
       </c>
       <c r="F52" s="3">
         <v>1600</v>
       </c>
       <c r="G52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H52" s="3">
         <v>1500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>28300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>31000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>33500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>33400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>28000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3">
         <v>100</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3962,8 +4082,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4042,74 +4165,77 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>927800</v>
+      </c>
+      <c r="E54" s="3">
         <v>906700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>792300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>724900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>716000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>745400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>775700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>772200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>768800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>757900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>773300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>734000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>778000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>859700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>887100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>896900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>890000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>277400</v>
-      </c>
-      <c r="U54" s="3">
-        <v>277800</v>
       </c>
       <c r="V54" s="3">
         <v>277800</v>
       </c>
       <c r="W54" s="3">
+        <v>277800</v>
+      </c>
+      <c r="X54" s="3">
         <v>200</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4122,8 +4248,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4152,8 +4281,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4182,61 +4312,62 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E57" s="3">
         <v>40000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>26400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>39500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>51400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>57400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>43700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>21400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>33100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>30600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>20700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>19900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11800</v>
-      </c>
-      <c r="T57" s="3">
-        <v>200</v>
       </c>
       <c r="U57" s="3">
         <v>200</v>
@@ -4245,10 +4376,10 @@
         <v>200</v>
       </c>
       <c r="W57" s="3">
-        <v>0</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="X57" s="3">
+        <v>0</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
@@ -4262,61 +4393,64 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3000</v>
+        <v>3800</v>
       </c>
       <c r="E58" s="3">
         <v>3000</v>
       </c>
       <c r="F58" s="3">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="G58" s="3">
         <v>3300</v>
       </c>
       <c r="H58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I58" s="3">
         <v>3500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10700</v>
-      </c>
-      <c r="K58" s="3">
-        <v>10500</v>
       </c>
       <c r="L58" s="3">
         <v>10500</v>
       </c>
       <c r="M58" s="3">
+        <v>10500</v>
+      </c>
+      <c r="N58" s="3">
         <v>7400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7700</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -4324,12 +4458,12 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3">
         <v>100</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,74 +4476,77 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>68800</v>
+      </c>
+      <c r="E59" s="3">
         <v>60200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>82000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>51600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>50300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>56600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>58000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>54300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>55000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>52700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>130600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>102500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>98100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>105800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>132900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>135000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>205700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>400</v>
-      </c>
-      <c r="U59" s="3">
-        <v>300</v>
       </c>
       <c r="V59" s="3">
         <v>300</v>
       </c>
       <c r="W59" s="3">
+        <v>300</v>
+      </c>
+      <c r="X59" s="3">
         <v>100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4422,61 +4559,64 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>167600</v>
+      </c>
+      <c r="E60" s="3">
         <v>170700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>201600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>149100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>144500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>174900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>182900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>174700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>148800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>144800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>171100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>140300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>118400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>134300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>152800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>146300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>217400</v>
-      </c>
-      <c r="T60" s="3">
-        <v>600</v>
       </c>
       <c r="U60" s="3">
         <v>600</v>
@@ -4485,11 +4625,11 @@
         <v>600</v>
       </c>
       <c r="W60" s="3">
+        <v>600</v>
+      </c>
+      <c r="X60" s="3">
         <v>100</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,52 +4642,55 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E61" s="3">
         <v>11400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7400</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>100</v>
       </c>
       <c r="R61" s="3">
         <v>100</v>
@@ -4556,7 +4699,7 @@
         <v>100</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -4582,8 +4725,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4602,41 +4748,41 @@
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>900</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>18300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>27000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>28000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>38400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>29900</v>
-      </c>
-      <c r="T62" s="3">
-        <v>9700</v>
       </c>
       <c r="U62" s="3">
         <v>9700</v>
@@ -4644,8 +4790,8 @@
       <c r="V62" s="3">
         <v>9700</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
+      <c r="W62" s="3">
+        <v>9700</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
@@ -4662,8 +4808,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4742,8 +4891,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4822,8 +4974,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4902,61 +5057,64 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>207600</v>
+      </c>
+      <c r="E66" s="3">
         <v>195800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>219900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>169600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>163600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>194900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>202700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>194800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>167500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>164000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>196500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>161100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>141200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>168700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>180900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>184800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>247400</v>
-      </c>
-      <c r="T66" s="3">
-        <v>10200</v>
       </c>
       <c r="U66" s="3">
         <v>10200</v>
@@ -4965,11 +5123,11 @@
         <v>10200</v>
       </c>
       <c r="W66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="X66" s="3">
         <v>100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4982,8 +5140,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5012,8 +5173,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5092,8 +5254,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5172,8 +5337,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5252,8 +5420,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5332,73 +5503,76 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1149700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1095700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1087500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1059300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1071800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1050000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1024500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-986000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-974400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-964100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-939000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-811200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-802300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-797500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-757300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-704000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-634100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-600</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-300</v>
       </c>
       <c r="V72" s="3">
         <v>-300</v>
       </c>
       <c r="W72" s="3">
-        <v>0</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="X72" s="3">
+        <v>0</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
@@ -5412,8 +5586,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5492,8 +5669,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5572,8 +5752,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5652,73 +5835,76 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>720100</v>
+      </c>
+      <c r="E76" s="3">
         <v>710800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>572400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>555300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>552400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>550500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>573000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>577400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>601300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>593900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>576800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>572900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>636800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>691100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>706200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>712100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>642600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>267200</v>
-      </c>
-      <c r="U76" s="3">
-        <v>267500</v>
       </c>
       <c r="V76" s="3">
         <v>267500</v>
       </c>
       <c r="W76" s="3">
-        <v>0</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
+        <v>267500</v>
+      </c>
+      <c r="X76" s="3">
+        <v>0</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
@@ -5732,8 +5918,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5812,79 +6001,82 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5897,73 +6089,76 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-21800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-127700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-64600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-70000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-464200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5300</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-300</v>
       </c>
       <c r="V81" s="3">
         <v>-300</v>
       </c>
       <c r="W81" s="3">
-        <v>0</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="X81" s="3">
+        <v>0</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
@@ -5977,8 +6172,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6007,73 +6205,74 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E83" s="3">
         <v>1300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>17100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>16700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>17300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>17500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>17400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>19500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10100</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -6087,8 +6286,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6167,8 +6369,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6247,8 +6452,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6327,8 +6535,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6407,8 +6618,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6487,73 +6701,76 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-30800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>86600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-18800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>23100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-25300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-34100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-29900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
+      <c r="X89" s="3">
+        <v>0</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
@@ -6567,8 +6784,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6597,73 +6817,74 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -6677,8 +6898,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6757,8 +6981,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6837,67 +7064,70 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-19500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-35200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-80500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4200</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -6908,8 +7138,8 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -6917,8 +7147,11 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6947,8 +7180,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6979,8 +7213,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7027,8 +7261,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7107,8 +7344,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7187,8 +7427,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7267,17 +7510,20 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>144000</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
@@ -7285,11 +7531,11 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-7600</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
@@ -7297,11 +7543,11 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-600</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -7312,28 +7558,28 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>1300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>33400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>375700</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>277600</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
+      <c r="X100" s="3">
+        <v>0</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
@@ -7347,73 +7593,76 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>18700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>18700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-10400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-9900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -7427,73 +7676,76 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E102" s="3">
         <v>100400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>66200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-23900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-33000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-27500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-24600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-48200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-11900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-41100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>264800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1500</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
+      <c r="X102" s="3">
+        <v>0</v>
       </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
@@ -7505,6 +7757,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="92">
   <si>
     <t>GENI</t>
   </si>
@@ -656,116 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
@@ -778,71 +778,74 @@
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>240500</v>
+      </c>
+      <c r="E8" s="3">
         <v>166300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>118700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>144000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>175500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>120200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>95400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>119700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>127200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>101700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>86800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>97200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>105300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>78700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>71100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>85900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>84000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>69100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>55800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>53700</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,8 +858,8 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC8" s="3">
         <v>0</v>
@@ -864,71 +867,74 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>172100</v>
+      </c>
+      <c r="E9" s="3">
         <v>125000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>109800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>108700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>128100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>80100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>67100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>106900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>116700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>77400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>62200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>87700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>102200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>72800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>61800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>101400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>109400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>86400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>240200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>40100</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -950,71 +956,74 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E10" s="3">
         <v>41300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>35300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>47400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>40100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>28400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-15500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-25400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-17300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-184400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>13600</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1036,8 +1045,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1068,71 +1080,72 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E12" s="3">
         <v>4900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3300</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,8 +1167,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1240,71 +1256,74 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E14" s="3">
         <v>12200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>12600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4100</v>
       </c>
-      <c r="G14" s="3">
-        <v>-1200</v>
-      </c>
       <c r="H14" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="I14" s="3">
         <v>3700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1500</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>6100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>700</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1317,8 +1336,8 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1326,47 +1345,50 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E15" s="3">
         <v>4600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>27600</v>
-      </c>
-      <c r="F15" s="3">
-        <v>4100</v>
       </c>
       <c r="G15" s="3">
         <v>4100</v>
       </c>
       <c r="H15" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I15" s="3">
         <v>8900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>30200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>24000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1412,8 +1434,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1441,79 +1466,80 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>284100</v>
+      </c>
+      <c r="E17" s="3">
         <v>179600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>186800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>160300</v>
       </c>
-      <c r="G17" s="3">
-        <v>183000</v>
-      </c>
       <c r="H17" s="3">
+        <v>188700</v>
+      </c>
+      <c r="I17" s="3">
         <v>122500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>113700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>142300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>161200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>109800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>94200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>119400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>150200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>112000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>110800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>150900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>160300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>133900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>485000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>56800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>300</v>
       </c>
-      <c r="Y17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
+      <c r="Z17" s="3">
+        <v>0</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
@@ -1527,71 +1553,74 @@
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-68100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16300</v>
       </c>
-      <c r="G18" s="3">
-        <v>-7500</v>
-      </c>
       <c r="H18" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="I18" s="3">
         <v>-2300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-18200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-22600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-34100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-22200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-44900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-33300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-39700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-65000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-76300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-64800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-429200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3100</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1613,8 +1642,11 @@
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1645,71 +1677,72 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E20" s="3">
         <v>5700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-27900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-12300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>25700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-23200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-81500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>25000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>35300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>25800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>11700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-34600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2500</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1731,71 +1764,74 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-33900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-14500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-12600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-29100</v>
-      </c>
       <c r="H21" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="I21" s="3">
         <v>29700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-15600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>18800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-109200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-21700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-47200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-50900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-451500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4600</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1817,46 +1853,49 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>1300</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
-        <v>400</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>400</v>
@@ -1867,11 +1906,11 @@
       <c r="R22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="S22" s="3">
+        <v>400</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1903,79 +1942,82 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-31400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-52200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-32100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-23100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-38900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-126700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-39600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-64600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-70500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-463800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5600</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-300</v>
       </c>
       <c r="X23" s="3">
         <v>-300</v>
       </c>
       <c r="Y23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>0</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
@@ -1989,76 +2031,79 @@
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-11300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-300</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
+      <c r="Y24" s="3">
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
@@ -2066,8 +2111,8 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
@@ -2075,8 +2120,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2161,79 +2209,82 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-28800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-53900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-28200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>12500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-21800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-38500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-127700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-40200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-53300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-70000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-464200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5300</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-300</v>
       </c>
       <c r="X26" s="3">
         <v>-300</v>
       </c>
       <c r="Y26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>0</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
@@ -2247,79 +2298,82 @@
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-53900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-21800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-38500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-127700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-40200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-64600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-70000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-464200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5300</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-300</v>
       </c>
       <c r="X27" s="3">
         <v>-300</v>
       </c>
       <c r="Y27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>0</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
@@ -2333,8 +2387,11 @@
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2419,8 +2476,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2505,8 +2565,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2591,8 +2654,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2677,71 +2743,74 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>27900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>12300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-25700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>23200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>81500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-35300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-25800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-11700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>34600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2500</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2763,79 +2832,82 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-28800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-53900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-21800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-38500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-127700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-40200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-64600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-70000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-464200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5300</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-300</v>
       </c>
       <c r="X33" s="3">
         <v>-300</v>
       </c>
       <c r="Y33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>0</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
@@ -2849,8 +2921,11 @@
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2935,79 +3010,82 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-28800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-53900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-21800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-38500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-127700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-40200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-64600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-70000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-464200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5300</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-300</v>
       </c>
       <c r="X35" s="3">
         <v>-300</v>
       </c>
       <c r="Y35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>0</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
@@ -3021,85 +3099,88 @@
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3112,8 +3193,11 @@
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3144,8 +3228,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3176,79 +3261,80 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>280600</v>
+      </c>
+      <c r="E41" s="3">
         <v>207800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>221600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>209800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>110200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>42300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>67700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>67500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>100300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>92000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>89800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>94400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>122700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>116900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>138500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>174200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>222400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>234200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>275300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1000</v>
-      </c>
-      <c r="W41" s="3">
-        <v>1500</v>
       </c>
       <c r="X41" s="3">
         <v>1500</v>
       </c>
       <c r="Y41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="Z41" s="3">
+        <v>0</v>
       </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
@@ -3262,8 +3348,11 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3283,13 +3372,13 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>5800</v>
       </c>
       <c r="K42" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -3348,68 +3437,71 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>201600</v>
+      </c>
+      <c r="E43" s="3">
         <v>200700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>135300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>122000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>124400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>128800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>98400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>131900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>116900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>105600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>99300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>82400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>73200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>69200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>56900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>89600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>77300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>66000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>57800</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3425,8 +3517,8 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -3434,13 +3526,16 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E44" s="3">
         <v>400</v>
@@ -3449,7 +3544,7 @@
         <v>400</v>
       </c>
       <c r="G44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H44" s="3">
         <v>500</v>
@@ -3458,49 +3553,49 @@
         <v>500</v>
       </c>
       <c r="J44" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="K44" s="3">
         <v>300</v>
       </c>
       <c r="L44" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M44" s="3">
         <v>400</v>
       </c>
       <c r="N44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O44" s="3">
         <v>300</v>
       </c>
       <c r="P44" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q44" s="3">
         <v>400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>300</v>
-      </c>
-      <c r="R44" s="3">
-        <v>500</v>
       </c>
       <c r="S44" s="3">
         <v>500</v>
       </c>
       <c r="T44" s="3">
+        <v>500</v>
+      </c>
+      <c r="U44" s="3">
         <v>600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>400</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
@@ -3520,13 +3615,16 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E45" s="3">
         <v>1200</v>
@@ -3535,11 +3633,11 @@
         <v>1200</v>
       </c>
       <c r="G45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H45" s="3">
         <v>1100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3558,38 +3656,38 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>40300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>51700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>37800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>29700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>24400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>33100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>400</v>
-      </c>
-      <c r="W45" s="3">
-        <v>200</v>
       </c>
       <c r="X45" s="3">
         <v>200</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
+      <c r="Y45" s="3">
+        <v>200</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
@@ -3606,79 +3704,82 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>549700</v>
+      </c>
+      <c r="E46" s="3">
         <v>466400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>395700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>396600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>288600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>224400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>222500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>229200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>244800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>248100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>222200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>218400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>236500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>238100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>233500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>294000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>324700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>333900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>344600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1400</v>
-      </c>
-      <c r="W46" s="3">
-        <v>1700</v>
       </c>
       <c r="X46" s="3">
         <v>1700</v>
       </c>
       <c r="Y46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
+        <v>1700</v>
+      </c>
+      <c r="Z46" s="3">
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
@@ -3692,76 +3793,79 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E47" s="3">
         <v>31800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>30000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>29300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>31700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>30700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>28900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>25000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>26400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>24700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>24000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>23000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>32800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>29400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>29300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>31100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3">
         <v>276100</v>
-      </c>
-      <c r="W47" s="3">
-        <v>276000</v>
       </c>
       <c r="X47" s="3">
         <v>276000</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
+      <c r="Y47" s="3">
+        <v>276000</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
@@ -3778,68 +3882,71 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E48" s="3">
         <v>58200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>54700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>34600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17700</v>
-      </c>
-      <c r="N48" s="3">
-        <v>19300</v>
       </c>
       <c r="O48" s="3">
         <v>19300</v>
       </c>
       <c r="P48" s="3">
+        <v>19300</v>
+      </c>
+      <c r="Q48" s="3">
         <v>11800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10400</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3855,8 +3962,8 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -3864,68 +3971,71 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>482300</v>
+      </c>
+      <c r="E49" s="3">
         <v>487700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>442300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>441300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>441600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>441100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>440500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>443100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>455700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>447200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>469500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>462000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>459100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>428900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>473600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>516700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>537600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>542500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>523100</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3941,8 +4051,8 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
@@ -3950,8 +4060,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4036,8 +4149,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4122,8 +4238,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4131,71 +4250,71 @@
         <v>2400</v>
       </c>
       <c r="E52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F52" s="3">
         <v>2500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1600</v>
       </c>
       <c r="H52" s="3">
         <v>1600</v>
       </c>
       <c r="I52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J52" s="3">
         <v>1500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>26600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>33500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>33400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>25800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>28000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12000</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3">
         <v>100</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4208,8 +4327,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4294,80 +4416,83 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1130300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1049100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>927800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>906700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>792300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>724900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>716000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>745400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>775700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>772200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>768800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>757900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>773300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>734000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>778000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>859700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>887100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>896900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>890000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>277400</v>
-      </c>
-      <c r="W54" s="3">
-        <v>277800</v>
       </c>
       <c r="X54" s="3">
         <v>277800</v>
       </c>
       <c r="Y54" s="3">
+        <v>277800</v>
+      </c>
+      <c r="Z54" s="3">
         <v>200</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4380,8 +4505,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4412,8 +4540,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4444,67 +4573,68 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E57" s="3">
         <v>59900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>40000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>36700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>26400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>39500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>51400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>57400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>43700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>23600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>21400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>33100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>30600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11800</v>
-      </c>
-      <c r="V57" s="3">
-        <v>200</v>
       </c>
       <c r="W57" s="3">
         <v>200</v>
@@ -4513,10 +4643,10 @@
         <v>200</v>
       </c>
       <c r="Y57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>0</v>
       </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
@@ -4530,67 +4660,70 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>3000</v>
       </c>
       <c r="G58" s="3">
         <v>3000</v>
       </c>
       <c r="H58" s="3">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="I58" s="3">
         <v>3300</v>
       </c>
       <c r="J58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K58" s="3">
         <v>3500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10700</v>
-      </c>
-      <c r="M58" s="3">
-        <v>10500</v>
       </c>
       <c r="N58" s="3">
         <v>10500</v>
       </c>
       <c r="O58" s="3">
+        <v>10500</v>
+      </c>
+      <c r="P58" s="3">
         <v>7400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7700</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
+      <c r="V58" s="3">
+        <v>0</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
@@ -4598,12 +4731,12 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3">
         <v>100</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4616,80 +4749,83 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>116800</v>
+      </c>
+      <c r="E59" s="3">
         <v>116900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>68800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>60200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>82000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>51600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>50300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>56600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>58000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>54300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>55000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>52700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>130600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>102500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>98100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>105800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>132900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>135000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>205700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>400</v>
-      </c>
-      <c r="W59" s="3">
-        <v>300</v>
       </c>
       <c r="X59" s="3">
         <v>300</v>
       </c>
       <c r="Y59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z59" s="3">
         <v>100</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4702,67 +4838,70 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>352900</v>
+      </c>
+      <c r="E60" s="3">
         <v>269300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>167600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>170700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>201600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>149100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>144500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>174900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>182900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>174700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>148800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>144800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>171100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>140300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>118400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>134300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>152800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>146300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>217400</v>
-      </c>
-      <c r="V60" s="3">
-        <v>600</v>
       </c>
       <c r="W60" s="3">
         <v>600</v>
@@ -4771,11 +4910,11 @@
         <v>600</v>
       </c>
       <c r="Y60" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z60" s="3">
         <v>100</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4788,58 +4927,61 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E61" s="3">
         <v>26100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>26800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7400</v>
-      </c>
-      <c r="S61" s="3">
-        <v>100</v>
       </c>
       <c r="T61" s="3">
         <v>100</v>
@@ -4848,7 +4990,7 @@
         <v>100</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -4874,17 +5016,20 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E62" s="3">
         <v>19400</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4900,41 +5045,41 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>900</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>18300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>27000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>28000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>38400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>29900</v>
-      </c>
-      <c r="V62" s="3">
-        <v>9700</v>
       </c>
       <c r="W62" s="3">
         <v>9700</v>
@@ -4942,8 +5087,8 @@
       <c r="X62" s="3">
         <v>9700</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
+      <c r="Y62" s="3">
+        <v>9700</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
@@ -4960,8 +5105,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5046,8 +5194,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5132,8 +5283,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5218,67 +5372,70 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>405800</v>
+      </c>
+      <c r="E66" s="3">
         <v>326600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>207600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>195800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>219900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>169600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>163600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>194900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>202700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>194800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>167500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>164000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>196500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>161100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>141200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>168700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>180900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>184800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>247400</v>
-      </c>
-      <c r="V66" s="3">
-        <v>10200</v>
       </c>
       <c r="W66" s="3">
         <v>10200</v>
@@ -5287,11 +5444,11 @@
         <v>10200</v>
       </c>
       <c r="Y66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="Z66" s="3">
         <v>100</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5304,8 +5461,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5336,8 +5496,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5422,8 +5583,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5508,8 +5672,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5594,8 +5761,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5680,79 +5850,82 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1199100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1178500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1149700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1095700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1087500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1059300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1071800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1050000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1024500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-986000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-974400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-964100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-939000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-811200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-802300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-797500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-757300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-704000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-634100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-600</v>
-      </c>
-      <c r="W72" s="3">
-        <v>-300</v>
       </c>
       <c r="X72" s="3">
         <v>-300</v>
       </c>
       <c r="Y72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="Z72" s="3">
+        <v>0</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
@@ -5766,8 +5939,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5852,8 +6028,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5938,8 +6117,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6024,79 +6206,82 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>724500</v>
+      </c>
+      <c r="E76" s="3">
         <v>722500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>720100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>710800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>572400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>555300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>552400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>550500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>573000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>577400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>601300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>593900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>576800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>572900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>636800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>691100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>706200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>712100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>642600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>267200</v>
-      </c>
-      <c r="W76" s="3">
-        <v>267500</v>
       </c>
       <c r="X76" s="3">
         <v>267500</v>
       </c>
       <c r="Y76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
+        <v>267500</v>
+      </c>
+      <c r="Z76" s="3">
+        <v>0</v>
       </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
@@ -6110,8 +6295,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6196,85 +6384,88 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6287,79 +6478,82 @@
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-28800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-53900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-21800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-38500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-127700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-40200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-64600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-70000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-464200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5300</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-300</v>
       </c>
       <c r="X81" s="3">
         <v>-300</v>
       </c>
       <c r="Y81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>0</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
@@ -6373,8 +6567,11 @@
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6405,79 +6602,80 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E83" s="3">
         <v>-15300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>17100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>17300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>17500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>17400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>19500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>10100</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -6491,8 +6689,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6577,8 +6778,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6663,8 +6867,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6749,8 +6956,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6835,8 +7045,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6921,79 +7134,82 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E89" s="3">
         <v>27200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-30800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>86600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>24000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-18800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>23100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-25300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-34100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-29900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
+      <c r="Z89" s="3">
+        <v>0</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
@@ -7007,8 +7223,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7039,79 +7258,80 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4100</v>
       </c>
-      <c r="G91" s="3">
-        <v>-1900</v>
-      </c>
       <c r="H91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I91" s="3">
         <v>-4900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -7125,8 +7345,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7211,8 +7434,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7297,73 +7523,76 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-38700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-19500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-35200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-80500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4200</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
+      <c r="X94" s="3">
+        <v>0</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
@@ -7374,8 +7603,8 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -7383,8 +7612,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7415,8 +7647,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7453,8 +7686,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7501,8 +7734,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7587,8 +7823,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7673,8 +7912,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7759,8 +8001,11 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7771,11 +8016,11 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>144000</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -7783,11 +8028,11 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-7600</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -7795,11 +8040,11 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-600</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
@@ -7810,28 +8055,28 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>1300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>33400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>375700</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>277600</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
@@ -7845,79 +8090,82 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>18700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-10400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>18700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-10400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-9900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
@@ -7931,79 +8179,82 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-13800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>100400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>66200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-23900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-33000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-16300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-27500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-48200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-41100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>264800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1500</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
+      <c r="Z102" s="3">
+        <v>0</v>
       </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
@@ -8015,6 +8266,9 @@
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GENI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>GENI</t>
   </si>
@@ -656,119 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
@@ -781,74 +782,77 @@
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E8" s="3">
         <v>240500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>166300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>118700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>144000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>175500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>120200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>95400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>119700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>127200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>101700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>86800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>97200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>105300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>78700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>71100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>85900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>84000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>69100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>55800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>53700</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -861,8 +865,8 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -870,74 +874,77 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>144600</v>
+      </c>
+      <c r="E9" s="3">
         <v>172100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>125000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>109800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>108700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>128100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>80100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>67100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>106900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>116700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>77400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>62200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>87700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>102200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>72800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>61800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>101400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>109400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>86400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>240200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>40100</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,74 +966,77 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E10" s="3">
         <v>68400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>41300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>35300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>47400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>40100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>28400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>24700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-15500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-25400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-17300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-184400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>13600</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1048,8 +1058,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1081,74 +1094,75 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E12" s="3">
         <v>8400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3300</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1170,8 +1184,11 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1259,74 +1276,77 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-19000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>12200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>12600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-6800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>6100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>700</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1339,8 +1359,8 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1348,50 +1368,53 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E15" s="3">
         <v>7100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>27600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>4100</v>
       </c>
       <c r="H15" s="3">
         <v>4100</v>
       </c>
       <c r="I15" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J15" s="3">
         <v>8900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>30200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>24000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>11000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1437,8 +1460,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1467,82 +1493,83 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>217600</v>
+      </c>
+      <c r="E17" s="3">
         <v>284100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>179600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>186800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>160300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>188700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>122500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>113700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>142300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>161200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>109800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>94200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>119400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>150200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>112000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>110800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>150900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>160300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>133900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>485000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>56800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>300</v>
       </c>
-      <c r="Z17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
+      <c r="AA17" s="3">
+        <v>0</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
@@ -1556,74 +1583,77 @@
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-43600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-68100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-18200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-22600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-34100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-22200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-44900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-33300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-39700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-65000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-76300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-64800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-429200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3100</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1645,8 +1675,11 @@
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1678,74 +1711,75 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-27900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-12300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>25700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-23200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-81500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>25000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>35300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>25800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>11700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-34600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2500</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1767,74 +1801,77 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-33900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-12600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-34800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>29700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-15600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-10700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-109200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-21700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-47200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-50900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-451500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4600</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1856,49 +1893,52 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>900</v>
+      </c>
+      <c r="E22" s="3">
         <v>5400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
         <v>1300</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3">
-        <v>400</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>400</v>
@@ -1909,11 +1949,11 @@
       <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="T22" s="3">
+        <v>400</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1945,82 +1985,85 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-55600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-22800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-31400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-52200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-32100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-23100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-38900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-126700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-39600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-64600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-70500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-463800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5600</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-300</v>
       </c>
       <c r="Y23" s="3">
         <v>-300</v>
       </c>
       <c r="Z23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>0</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
@@ -2034,79 +2077,82 @@
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-11300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-300</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
@@ -2114,8 +2160,8 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -2123,8 +2169,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2212,82 +2261,85 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-20600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-53900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-28200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>12500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-21800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-38500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-11600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-25200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-127700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-40200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-53300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-70000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-464200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5300</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-300</v>
       </c>
       <c r="Y26" s="3">
         <v>-300</v>
       </c>
       <c r="Z26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>0</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
@@ -2301,82 +2353,85 @@
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-20600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-53900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-28200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-21800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-38500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-25200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-127700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-40200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-64600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-70000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-464200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5300</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-300</v>
       </c>
       <c r="Y27" s="3">
         <v>-300</v>
       </c>
       <c r="Z27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>0</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
@@ -2390,8 +2445,11 @@
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2479,8 +2537,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2568,8 +2629,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2657,8 +2721,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2746,74 +2813,77 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E32" s="3">
         <v>2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>27900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>12300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-25700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>23200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>81500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-25000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-35300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-25800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-11700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>34600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2500</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,82 +2905,85 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-20600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-53900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-28200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-21800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-38500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-25200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-127700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-40200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-64600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-70000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-464200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5300</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-300</v>
       </c>
       <c r="Y33" s="3">
         <v>-300</v>
       </c>
       <c r="Z33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>0</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
@@ -2924,8 +2997,11 @@
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3013,82 +3089,85 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-20600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-53900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-28200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-21800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-38500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-25200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-127700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-40200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-64600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-70000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-464200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5300</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-300</v>
       </c>
       <c r="Y35" s="3">
         <v>-300</v>
       </c>
       <c r="Z35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>0</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
@@ -3102,88 +3181,91 @@
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3196,8 +3278,11 @@
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3229,8 +3314,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3262,82 +3348,83 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>197400</v>
+      </c>
+      <c r="E41" s="3">
         <v>280600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>207800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>221600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>209800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>110200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>42300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>67700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>67500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>92000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>89800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>94400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>122700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>116900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>138500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>174200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>222400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>234200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>275300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1000</v>
-      </c>
-      <c r="X41" s="3">
-        <v>1500</v>
       </c>
       <c r="Y41" s="3">
         <v>1500</v>
       </c>
       <c r="Z41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>0</v>
       </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
@@ -3351,8 +3438,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3375,13 +3465,13 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>5800</v>
       </c>
       <c r="L42" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -3440,71 +3530,74 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>173600</v>
+      </c>
+      <c r="E43" s="3">
         <v>201600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>200700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>135300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>122000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>124400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>128800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>98400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>131900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>116900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>105600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>99300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>82400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>73200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>69200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>56900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>89600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>77300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>66000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>57800</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3520,8 +3613,8 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -3529,16 +3622,19 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>400</v>
+      </c>
+      <c r="E44" s="3">
         <v>300</v>
-      </c>
-      <c r="E44" s="3">
-        <v>400</v>
       </c>
       <c r="F44" s="3">
         <v>400</v>
@@ -3547,7 +3643,7 @@
         <v>400</v>
       </c>
       <c r="H44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I44" s="3">
         <v>500</v>
@@ -3556,49 +3652,49 @@
         <v>500</v>
       </c>
       <c r="K44" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="L44" s="3">
         <v>300</v>
       </c>
       <c r="M44" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N44" s="3">
         <v>400</v>
       </c>
       <c r="O44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P44" s="3">
         <v>300</v>
       </c>
       <c r="Q44" s="3">
+        <v>300</v>
+      </c>
+      <c r="R44" s="3">
         <v>400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>300</v>
-      </c>
-      <c r="S44" s="3">
-        <v>500</v>
       </c>
       <c r="T44" s="3">
         <v>500</v>
       </c>
       <c r="U44" s="3">
+        <v>500</v>
+      </c>
+      <c r="V44" s="3">
         <v>600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>400</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
@@ -3618,16 +3714,19 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1200</v>
       </c>
       <c r="F45" s="3">
         <v>1200</v>
@@ -3636,11 +3735,11 @@
         <v>1200</v>
       </c>
       <c r="H45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,38 +3758,38 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>40300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>51700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>37800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>24400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>33100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>11100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>400</v>
-      </c>
-      <c r="X45" s="3">
-        <v>200</v>
       </c>
       <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
+      <c r="Z45" s="3">
+        <v>200</v>
       </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
@@ -3707,82 +3806,85 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>437200</v>
+      </c>
+      <c r="E46" s="3">
         <v>549700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>466400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>395700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>396600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>288600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>224400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>222500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>229200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>244800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>248100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>222200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>218400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>236500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>238100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>233500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>294000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>324700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>333900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>344600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1400</v>
-      </c>
-      <c r="X46" s="3">
-        <v>1700</v>
       </c>
       <c r="Y46" s="3">
         <v>1700</v>
       </c>
       <c r="Z46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
+        <v>1700</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>0</v>
       </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
@@ -3796,79 +3898,82 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E47" s="3">
         <v>32600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>31800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>30000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>29300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>31700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>30700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>25000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>26400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>24700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>24000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>23000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>32800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>29400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>29300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>31100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3">
         <v>276100</v>
-      </c>
-      <c r="X47" s="3">
-        <v>276000</v>
       </c>
       <c r="Y47" s="3">
         <v>276000</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
+      <c r="Z47" s="3">
+        <v>276000</v>
       </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
@@ -3885,71 +3990,74 @@
       <c r="AE47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E48" s="3">
         <v>60600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>58200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>54700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17700</v>
-      </c>
-      <c r="O48" s="3">
-        <v>19300</v>
       </c>
       <c r="P48" s="3">
         <v>19300</v>
       </c>
       <c r="Q48" s="3">
+        <v>19300</v>
+      </c>
+      <c r="R48" s="3">
         <v>11800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>14400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10400</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3965,8 +4073,8 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -3974,71 +4082,74 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>481100</v>
+      </c>
+      <c r="E49" s="3">
         <v>482300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>487700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>442300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>441300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>441600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>441100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>440500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>443100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>455700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>447200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>469500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>462000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>459100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>428900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>473600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>516700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>537600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>542500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>523100</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4054,8 +4165,8 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -4063,8 +4174,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4152,8 +4266,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4241,8 +4358,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4253,71 +4373,71 @@
         <v>2400</v>
       </c>
       <c r="F52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G52" s="3">
         <v>2500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1600</v>
       </c>
       <c r="I52" s="3">
         <v>1600</v>
       </c>
       <c r="J52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K52" s="3">
         <v>1500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>26600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>33500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>33400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>25600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>25800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>28000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="3">
         <v>100</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4330,8 +4450,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4419,83 +4542,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1017700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1130300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1049100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>927800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>906700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>792300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>724900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>716000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>745400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>775700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>772200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>768800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>757900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>773300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>734000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>778000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>859700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>887100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>896900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>890000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>277400</v>
-      </c>
-      <c r="X54" s="3">
-        <v>277800</v>
       </c>
       <c r="Y54" s="3">
         <v>277800</v>
       </c>
       <c r="Z54" s="3">
+        <v>277800</v>
+      </c>
+      <c r="AA54" s="3">
         <v>200</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4508,8 +4634,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4541,8 +4670,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4574,70 +4704,71 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E57" s="3">
         <v>112200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>59900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>40000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>36700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>26400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>39500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>51400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>57400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>43700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>23600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>21400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>33100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>30600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>20700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11800</v>
-      </c>
-      <c r="W57" s="3">
-        <v>200</v>
       </c>
       <c r="X57" s="3">
         <v>200</v>
@@ -4646,10 +4777,10 @@
         <v>200</v>
       </c>
       <c r="Z57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>0</v>
       </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
@@ -4663,8 +4794,11 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4672,61 +4806,61 @@
         <v>5000</v>
       </c>
       <c r="E58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F58" s="3">
         <v>4100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>3000</v>
       </c>
       <c r="H58" s="3">
         <v>3000</v>
       </c>
       <c r="I58" s="3">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="J58" s="3">
         <v>3300</v>
       </c>
       <c r="K58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L58" s="3">
         <v>3500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10700</v>
-      </c>
-      <c r="N58" s="3">
-        <v>10500</v>
       </c>
       <c r="O58" s="3">
         <v>10500</v>
       </c>
       <c r="P58" s="3">
+        <v>10500</v>
+      </c>
+      <c r="Q58" s="3">
         <v>7400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7700</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
@@ -4734,12 +4868,12 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA58" s="3">
         <v>100</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4752,83 +4886,86 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E59" s="3">
         <v>116800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>116900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>68800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>60200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>82000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>51600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>50300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>56600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>58000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>54300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>55000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>52700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>130600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>102500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>98100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>105800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>132900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>135000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>205700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>400</v>
-      </c>
-      <c r="X59" s="3">
-        <v>300</v>
       </c>
       <c r="Y59" s="3">
         <v>300</v>
       </c>
       <c r="Z59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA59" s="3">
         <v>100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4841,70 +4978,73 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>274000</v>
+      </c>
+      <c r="E60" s="3">
         <v>352900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>269300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>167600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>170700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>201600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>149100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>144500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>174900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>182900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>174700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>148800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>144800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>171100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>140300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>118400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>134300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>152800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>146300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>217400</v>
-      </c>
-      <c r="W60" s="3">
-        <v>600</v>
       </c>
       <c r="X60" s="3">
         <v>600</v>
@@ -4913,11 +5053,11 @@
         <v>600</v>
       </c>
       <c r="Z60" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA60" s="3">
         <v>100</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4930,8 +5070,11 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4939,52 +5082,52 @@
         <v>25500</v>
       </c>
       <c r="E61" s="3">
+        <v>25500</v>
+      </c>
+      <c r="F61" s="3">
         <v>26100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>26800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7400</v>
-      </c>
-      <c r="T61" s="3">
-        <v>100</v>
       </c>
       <c r="U61" s="3">
         <v>100</v>
@@ -4993,7 +5136,7 @@
         <v>100</v>
       </c>
       <c r="W61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X61" s="3">
         <v>0</v>
@@ -5019,20 +5162,23 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E62" s="3">
         <v>20300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>19400</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5048,41 +5194,41 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>900</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>18300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>27000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>28000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>38400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>29900</v>
-      </c>
-      <c r="W62" s="3">
-        <v>9700</v>
       </c>
       <c r="X62" s="3">
         <v>9700</v>
@@ -5090,8 +5236,8 @@
       <c r="Y62" s="3">
         <v>9700</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
+      <c r="Z62" s="3">
+        <v>9700</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
@@ -5108,8 +5254,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5197,8 +5346,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5286,8 +5438,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5375,70 +5530,73 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>322600</v>
+      </c>
+      <c r="E66" s="3">
         <v>405800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>326600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>207600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>195800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>219900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>169600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>163600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>194900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>202700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>194800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>167500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>164000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>196500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>161100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>141200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>168700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>180900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>184800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>247400</v>
-      </c>
-      <c r="W66" s="3">
-        <v>10200</v>
       </c>
       <c r="X66" s="3">
         <v>10200</v>
@@ -5447,11 +5605,11 @@
         <v>10200</v>
       </c>
       <c r="Z66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="AA66" s="3">
         <v>100</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5464,8 +5622,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5497,8 +5658,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5586,8 +5748,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5675,8 +5840,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5764,8 +5932,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5853,82 +6024,85 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1254600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1199100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1178500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1149700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1095700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1087500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1059300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1071800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1050000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1024500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-986000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-974400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-964100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-939000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-811200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-802300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-797500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-757300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-704000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-634100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-600</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-300</v>
       </c>
       <c r="Y72" s="3">
         <v>-300</v>
       </c>
       <c r="Z72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="AA72" s="3">
+        <v>0</v>
       </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
@@ -5942,8 +6116,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6031,8 +6208,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6120,8 +6300,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6209,82 +6392,85 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>695100</v>
+      </c>
+      <c r="E76" s="3">
         <v>724500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>722500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>720100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>710800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>572400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>555300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>552400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>550500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>573000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>577400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>601300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>593900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>576800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>572900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>636800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>691100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>706200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>712100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>642600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>267200</v>
-      </c>
-      <c r="X76" s="3">
-        <v>267500</v>
       </c>
       <c r="Y76" s="3">
         <v>267500</v>
       </c>
       <c r="Z76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
+        <v>267500</v>
+      </c>
+      <c r="AA76" s="3">
+        <v>0</v>
       </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
@@ -6298,8 +6484,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6387,88 +6576,91 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6481,82 +6673,85 @@
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-20600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-53900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-28200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-21800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-38500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-25200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-127700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-40200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-64600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-70000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-464200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5300</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-300</v>
       </c>
       <c r="Y81" s="3">
         <v>-300</v>
       </c>
       <c r="Z81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="AA81" s="3">
+        <v>0</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
@@ -6570,8 +6765,11 @@
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6603,82 +6801,83 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-15300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>17100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>16700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>17300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>17500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>17400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>19500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>10100</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -6692,8 +6891,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6781,8 +6983,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6870,8 +7075,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6959,8 +7167,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7048,8 +7259,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7137,82 +7351,85 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-66400</v>
+      </c>
+      <c r="E89" s="3">
         <v>89000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>27200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>86600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>24000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-18800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>23100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-25300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-34100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-29900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
+      <c r="AA89" s="3">
+        <v>0</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
@@ -7226,8 +7443,11 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7259,82 +7479,83 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -7348,8 +7569,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7437,8 +7661,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7526,76 +7753,79 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-38700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-19500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-35200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-80500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4200</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
@@ -7606,8 +7836,8 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -7615,8 +7845,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7648,8 +7881,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7689,8 +7923,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7737,8 +7971,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7826,8 +8063,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7915,8 +8155,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8004,13 +8247,16 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -8019,11 +8265,11 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>144000</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -8031,11 +8277,11 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-7600</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -8043,11 +8289,11 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-600</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
@@ -8058,28 +8304,28 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>1300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>33400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>375700</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>277600</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
+      <c r="AA100" s="3">
+        <v>0</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
@@ -8093,82 +8339,85 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>18700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-10400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>18700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-10400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -8182,82 +8431,85 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-83100</v>
+      </c>
+      <c r="E102" s="3">
         <v>72800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>100400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>66200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-23900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-33000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-27500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-24600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-48200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-11900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-41100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>264800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1500</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
+      <c r="AA102" s="3">
+        <v>0</v>
       </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
@@ -8269,6 +8521,9 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
